--- a/2022 data/excel_outputs/302_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/302_boothwise_data.xlsx
@@ -14,390 +14,1260 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="516" uniqueCount="441">
   <si>
     <t>AC 302 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
+    <t>Unnamed: 24</t>
+  </si>
+  <si>
+    <t>Unnamed: 25</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
     <t>POLLING STATION NAME</t>
   </si>
   <si>
-    <t>####0##0 #######</t>
-  </si>
-  <si>
-    <t>####0##0##########</t>
-  </si>
-  <si>
-    <t>####0##0####</t>
-  </si>
-  <si>
-    <t>####0##0#####</t>
-  </si>
-  <si>
-    <t>##0##0##0#######</t>
-  </si>
-  <si>
-    <t>####0##0########</t>
-  </si>
-  <si>
-    <t>##### ### #######</t>
-  </si>
-  <si>
-    <t>##### ### ########</t>
-  </si>
-  <si>
-    <t>##### ### ######</t>
-  </si>
-  <si>
-    <t>##### ### ###### #####</t>
-  </si>
-  <si>
-    <t>##### ### ###### #######</t>
-  </si>
-  <si>
-    <t>##### ### ######## #######</t>
-  </si>
-  <si>
-    <t>#0####0##0 ######### ##### ####</t>
-  </si>
-  <si>
-    <t>##### ### #####</t>
-  </si>
-  <si>
-    <t>##### ### #########</t>
-  </si>
-  <si>
-    <t>####0### ###### ##### #######</t>
-  </si>
-  <si>
-    <t>##### ### #### #### ######</t>
-  </si>
-  <si>
-    <t>##### ### ####### #####</t>
-  </si>
-  <si>
-    <t>##0##0### ###### #### ######</t>
-  </si>
-  <si>
-    <t>##0## ##### #### #######</t>
-  </si>
-  <si>
-    <t>##0##0### ##### #### #######</t>
-  </si>
-  <si>
-    <t>####0### #####</t>
-  </si>
-  <si>
-    <t>##### ### ##### #### ######</t>
-  </si>
-  <si>
-    <t>##### ### ##########</t>
-  </si>
-  <si>
-    <t>#### ##### ######## ####</t>
-  </si>
-  <si>
-    <t>##### ### ##### #######</t>
-  </si>
-  <si>
-    <t>##### ### ##### #### ########</t>
-  </si>
-  <si>
-    <t>####0### ######</t>
-  </si>
-  <si>
-    <t>####0### ####</t>
-  </si>
-  <si>
-    <t>##0##0### ###### #### #####</t>
-  </si>
-  <si>
-    <t>####0### #######</t>
-  </si>
-  <si>
-    <t>##### ### ####</t>
-  </si>
-  <si>
-    <t>####0### ######### #### #######</t>
-  </si>
-  <si>
-    <t>##0##0### #######</t>
-  </si>
-  <si>
-    <t>####0### ########</t>
-  </si>
-  <si>
-    <t>####0### #########</t>
-  </si>
-  <si>
-    <t>##0##0### ###### ##### #######</t>
-  </si>
-  <si>
-    <t>##### ### ##### ########</t>
-  </si>
-  <si>
-    <t>##0##0### ####</t>
-  </si>
-  <si>
-    <t>##0##0 ### #######</t>
-  </si>
-  <si>
-    <t>####### #### ######## ####</t>
-  </si>
-  <si>
-    <t>##0##0### ######</t>
-  </si>
-  <si>
-    <t>##0##0### ##### #######</t>
-  </si>
-  <si>
-    <t>##### ### ######## #### #####</t>
-  </si>
-  <si>
-    <t>##### ### #### #### #######</t>
-  </si>
-  <si>
-    <t>##### ### ######## #### ######### ##### #######</t>
-  </si>
-  <si>
-    <t>######## ###### ##### ######## #### #########</t>
-  </si>
-  <si>
-    <t>####0### ##### ##########</t>
-  </si>
-  <si>
-    <t>##### ### ######## ########</t>
-  </si>
-  <si>
-    <t>##### ### ####### ######</t>
-  </si>
-  <si>
-    <t>####0### #### ##### ####</t>
-  </si>
-  <si>
-    <t>##### ### ######## ######</t>
-  </si>
-  <si>
-    <t>####0 ##0 ### ########</t>
-  </si>
-  <si>
-    <t>##### ### #### ###</t>
-  </si>
-  <si>
-    <t>##### ### ####### #######</t>
-  </si>
-  <si>
-    <t>### ###### ######## #0### ### ####### ######</t>
-  </si>
-  <si>
-    <t>##0## ###### #####</t>
-  </si>
-  <si>
-    <t>##### ### ###### #### ######</t>
-  </si>
-  <si>
-    <t>#### ### #### ##0##0##### ####</t>
-  </si>
-  <si>
-    <t>####0### #### #### ######</t>
-  </si>
-  <si>
-    <t>######## #### #####</t>
-  </si>
-  <si>
-    <t>####0### ####### #### #######</t>
-  </si>
-  <si>
-    <t>##### ### ###########</t>
-  </si>
-  <si>
-    <t>####0##0 ########## #### ########</t>
-  </si>
-  <si>
-    <t>####0##0 ######</t>
-  </si>
-  <si>
-    <t>####0### #### ####### ######## #### #########</t>
-  </si>
-  <si>
-    <t>####0### #### ##### ###### ###</t>
-  </si>
-  <si>
-    <t>####0### ####### ######</t>
-  </si>
-  <si>
-    <t>####0### ###### #### #####</t>
-  </si>
-  <si>
-    <t>####0### ##### #######</t>
-  </si>
-  <si>
-    <t>####0### ##### ####### #######</t>
-  </si>
-  <si>
-    <t>##0## ##### #####</t>
-  </si>
-  <si>
-    <t>##0## #####</t>
-  </si>
-  <si>
-    <t>##0##0### #####</t>
-  </si>
-  <si>
-    <t>##0##0##### ######### ##### ######</t>
-  </si>
-  <si>
-    <t>########## #### ##0##0### ###### #######</t>
-  </si>
-  <si>
-    <t>####0### ######### #######</t>
-  </si>
-  <si>
-    <t>####0### ###### #####</t>
-  </si>
-  <si>
-    <t>####0### ###### #### #######</t>
-  </si>
-  <si>
-    <t>####0##0######</t>
-  </si>
-  <si>
-    <t>##0## ####</t>
-  </si>
-  <si>
-    <t>####0### ##### ######</t>
-  </si>
-  <si>
-    <t>##0##0### ####### ######</t>
-  </si>
-  <si>
-    <t>####0### ###### ######</t>
-  </si>
-  <si>
-    <t>##0##0##0 #####</t>
-  </si>
-  <si>
-    <t>####0### ##### ####</t>
-  </si>
-  <si>
-    <t>##### #0##0########## ##### ####</t>
-  </si>
-  <si>
-    <t>##0##0### ####### ##### ######</t>
-  </si>
-  <si>
-    <t>###### ##### ##### #######</t>
-  </si>
-  <si>
-    <t>####### ######## #######</t>
-  </si>
-  <si>
-    <t>####0### #### ######</t>
-  </si>
-  <si>
-    <t>##0##0##0####### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #######</t>
-  </si>
-  <si>
-    <t>####0### ####### ##### #####</t>
-  </si>
-  <si>
-    <t>####0### ###### ####</t>
-  </si>
-  <si>
-    <t>######## ###### ####0### #######</t>
-  </si>
-  <si>
-    <t>######## ####### #######</t>
-  </si>
-  <si>
-    <t>####0### ####### #####</t>
-  </si>
-  <si>
-    <t>##0##0### ####### ####</t>
-  </si>
-  <si>
-    <t>####0##0 #####</t>
-  </si>
-  <si>
-    <t>####0##0 ####</t>
-  </si>
-  <si>
-    <t>##0##0### ########</t>
-  </si>
-  <si>
-    <t>####0### ##########</t>
-  </si>
-  <si>
-    <t>####0### ##### ##### ##### ######</t>
-  </si>
-  <si>
-    <t>#### ####### ######</t>
-  </si>
-  <si>
-    <t>####0### ######### ##### #####</t>
-  </si>
-  <si>
-    <t>####0### ####### ###### #######</t>
-  </si>
-  <si>
-    <t>####0### ###### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ######</t>
-  </si>
-  <si>
-    <t>####0### ##### #####</t>
-  </si>
-  <si>
-    <t>####0 ##0 #########</t>
-  </si>
-  <si>
-    <t>##0##0##0######</t>
-  </si>
-  <si>
-    <t>##### ### #### #####</t>
-  </si>
-  <si>
-    <t>######## ###### #######</t>
-  </si>
-  <si>
-    <t>##### ### ######## ###</t>
-  </si>
-  <si>
-    <t>####### #####</t>
-  </si>
-  <si>
-    <t>######## ########</t>
-  </si>
-  <si>
-    <t>######## #######</t>
-  </si>
-  <si>
-    <t>##### ##0 #######</t>
-  </si>
-  <si>
-    <t>##### ### ##### ###</t>
-  </si>
-  <si>
-    <t>######## ##### #####</t>
-  </si>
-  <si>
-    <t>##### ### ##### #####</t>
-  </si>
-  <si>
-    <t>######### ##### #####</t>
-  </si>
-  <si>
-    <t>##### ### ###### ####</t>
-  </si>
-  <si>
-    <t>######## ####</t>
+    <t>CHE UMSAHAMIPAM</t>
+  </si>
+  <si>
+    <t>CHE UPEITAMNASAPALAM</t>
+  </si>
+  <si>
+    <t>CHE UMKADAP</t>
+  </si>
+  <si>
+    <t>CHE HIMTANUMT</t>
+  </si>
+  <si>
+    <t>CHE HAMRAMIMKAP NAT IUMKIUMDAMHAMT</t>
+  </si>
+  <si>
+    <t>CHE CHMTEIVIPALAM</t>
+  </si>
+  <si>
+    <t>CHE IMPATAPIMUM SAS</t>
+  </si>
+  <si>
+    <t>CHE RAPALAMIIMTAP</t>
+  </si>
+  <si>
+    <t>CHE AMSALAMD DAMHAMT NAT IITAPAKAMLADAMHAMT</t>
+  </si>
+  <si>
+    <t>CHAI AIMATAMNATAM</t>
+  </si>
+  <si>
+    <t>CHE KIMAMITAP AINATAK</t>
+  </si>
+  <si>
+    <t>CHE KIMAMITAP INARANATAH</t>
+  </si>
+  <si>
+    <t>CHE UMIMKAMA AINATAK</t>
+  </si>
+  <si>
+    <t>CHE CHAMTEM</t>
+  </si>
+  <si>
+    <t>CHE IMPATAPAM</t>
+  </si>
+  <si>
+    <t>CHE RAMUKIMTAM</t>
+  </si>
+  <si>
+    <t>CHE AINATINATAPALAM</t>
+  </si>
+  <si>
+    <t>CHE CHAMJIMTAKAMAPALAM</t>
+  </si>
+  <si>
+    <t>CHE MATAMITAM</t>
+  </si>
+  <si>
+    <t>CHE CHAMATAPIMUM</t>
+  </si>
+  <si>
+    <t>CHE CHAMATAPIUM</t>
+  </si>
+  <si>
+    <t>P.S. JHAKAHIYA</t>
+  </si>
+  <si>
+    <t>P.S. SONNAGAR</t>
+  </si>
+  <si>
+    <t>P.S. JIGINAMAFI</t>
+  </si>
+  <si>
+    <t>P.S. DEVARIYA</t>
+  </si>
+  <si>
+    <t>P.S. PATNA</t>
+  </si>
+  <si>
+    <t>P.S. CHAUKHARIYA</t>
+  </si>
+  <si>
+    <t>P.S. POKHARBHITWA</t>
+  </si>
+  <si>
+    <t>P.S. SIKRI</t>
+  </si>
+  <si>
+    <t>P.M.V. BELAHSA</t>
+  </si>
+  <si>
+    <t>P.S. BELAHSA</t>
+  </si>
+  <si>
+    <t>P.S. SANGRAMPUR</t>
+  </si>
+  <si>
+    <t>P.S. DABRA</t>
+  </si>
+  <si>
+    <t>P.S. PAKRI SHUKLA</t>
+  </si>
+  <si>
+    <t>P.S. BHAGAUSA</t>
+  </si>
+  <si>
+    <t>P.S. GAURA</t>
+  </si>
+  <si>
+    <t>P.S. PIPRI</t>
+  </si>
+  <si>
+    <t>P.S. PAKRAILA</t>
+  </si>
+  <si>
+    <t>P.S. SISWA BUZURG</t>
+  </si>
+  <si>
+    <t>P.S. BIRWAPUR</t>
+  </si>
+  <si>
+    <t>P.M.V. RANIJOT</t>
+  </si>
+  <si>
+    <t>P.S. MEHDANI</t>
+  </si>
+  <si>
+    <t>P.S. BAHUTI</t>
+  </si>
+  <si>
+    <t>P.S. SAURAHWA GRANT</t>
+  </si>
+  <si>
+    <t>P.S. BAGAHWA GRANT</t>
+  </si>
+  <si>
+    <t>P.S. GURAUAJOT GRANT</t>
+  </si>
+  <si>
+    <t>P.S. VISUNPUR KALA</t>
+  </si>
+  <si>
+    <t>P.S. EKDENGWA</t>
+  </si>
+  <si>
+    <t>S.S.S. TAKIYA</t>
+  </si>
+  <si>
+    <t>P.S. BHOPLAPUR</t>
+  </si>
+  <si>
+    <t>P.S. KAMHARIYA</t>
+  </si>
+  <si>
+    <t>P.S. SEMRI</t>
+  </si>
+  <si>
+    <t>P.M.V. SEMRI</t>
+  </si>
+  <si>
+    <t>P.S. PACHPERWA</t>
+  </si>
+  <si>
+    <t>P.S. PACHMOHANI</t>
+  </si>
+  <si>
+    <t>P.S. REHRA KALA</t>
+  </si>
+  <si>
+    <t>P.S. PARSA</t>
+  </si>
+  <si>
+    <t>P.S. RASOOLPUR</t>
+  </si>
+  <si>
+    <t>P.S. KATHELA SHARKI</t>
+  </si>
+  <si>
+    <t>P.S. KATHELA GARVI</t>
+  </si>
+  <si>
+    <t>P.M.V. KATHELA GARVI</t>
+  </si>
+  <si>
+    <t>P.S. CHECHRAF BUZURG</t>
+  </si>
+  <si>
+    <t>P.S. BHAISAHI JUNGLE</t>
+  </si>
+  <si>
+    <t>P.S. BANDUARI</t>
+  </si>
+  <si>
+    <t>P.S. BAIRIYA KHALSA</t>
+  </si>
+  <si>
+    <t>P.S. KHAKHARA</t>
+  </si>
+  <si>
+    <t>CHE AIMPATAP EIMAMAJAMS CHATAMEMK</t>
+  </si>
+  <si>
+    <t>CHE JAMSANADAKAM S</t>
+  </si>
+  <si>
+    <t>CHE JAMSANADAKAM SAS</t>
+  </si>
+  <si>
+    <t>CHE AIMRANATAPALAM EIMTAP</t>
+  </si>
+  <si>
+    <t>RIE UMJAPALAMT IINAJAMIUM</t>
+  </si>
+  <si>
+    <t>CHE KIMAIMTANUM</t>
+  </si>
+  <si>
+    <t>CH IIMUMD TAMAIMJ JAVASAM DAMRAMTAHAMKUM</t>
+  </si>
+  <si>
+    <t>RIE EPEUM NAT IEIPAIIMTAP</t>
+  </si>
+  <si>
+    <t>CHE IIMTAMNASAP</t>
+  </si>
+  <si>
+    <t>CHE MNATAMIUM</t>
+  </si>
+  <si>
+    <t>CHE CHAPAMNATAM</t>
+  </si>
+  <si>
+    <t>CHE IMENAKAP NTTH HAMRAMIMKAP</t>
+  </si>
+  <si>
+    <t>CHE EMAMATAM S</t>
+  </si>
+  <si>
+    <t>CHE KNAKIUMDAPALAM THANRANATAH</t>
+  </si>
+  <si>
+    <t>CHE UNARAMIDAM</t>
+  </si>
+  <si>
+    <t>CHE UNATAPASAM</t>
+  </si>
+  <si>
+    <t>LAMDAKIP |KAMTEI TAPAKALAMSAML THAMTIDAP</t>
+  </si>
+  <si>
+    <t>CHE KIMDAVATAM INARANATAH</t>
+  </si>
+  <si>
+    <t>CHE RAPAHADAPIMUM NTTH KIMDAVATAP</t>
+  </si>
+  <si>
+    <t>CHE IMTAHAMKUM</t>
+  </si>
+  <si>
+    <t>CHE JAMAMEMU</t>
+  </si>
+  <si>
+    <t>CHE CHAPACHATAM</t>
+  </si>
+  <si>
+    <t>RIE IIMACHANAT NAT IHANASAMTAP</t>
+  </si>
+  <si>
+    <t>CHE EMAUTAMIUM</t>
+  </si>
+  <si>
+    <t>CHE HIVATAMP NAT ITAVAPADAPIMUM</t>
+  </si>
+  <si>
+    <t>CHE UMIMKAMU INARANATAH</t>
+  </si>
+  <si>
+    <t>CHE IMHAMIP</t>
+  </si>
+  <si>
+    <t>SHRABHAIMNAKAMIP</t>
+  </si>
+  <si>
+    <t>CHE CHAMBIMNAKI</t>
+  </si>
+  <si>
+    <t>CHE TAMAKUMTAPALAM</t>
+  </si>
+  <si>
+    <t>CHE UMDACHANAT</t>
+  </si>
+  <si>
+    <t>CHE IMEMUMD CHAMAMT NAT IUMKATAMIPALAM</t>
+  </si>
+  <si>
+    <t>SHRABHAI MIPATAMNASAM</t>
+  </si>
+  <si>
+    <t>CHE IMEMDAJACHANAT</t>
+  </si>
+  <si>
+    <t>CHE IMDABIMNATAP</t>
+  </si>
+  <si>
+    <t>CHE AIMTAPAMNATAM</t>
+  </si>
+  <si>
+    <t>CHE IVIMSAP</t>
+  </si>
+  <si>
+    <t>CHE BIMDAKAMP</t>
+  </si>
+  <si>
+    <t>CHE SAVIMJAP</t>
+  </si>
+  <si>
+    <t>CHE BIMTAPAHAMUM</t>
+  </si>
+  <si>
+    <t>CHE RAVAIANADAKAM</t>
+  </si>
+  <si>
+    <t>CHE AVAJAPALAM</t>
+  </si>
+  <si>
+    <t>JHS DHANDHARA STHIT ADWADEEH</t>
+  </si>
+  <si>
+    <t>CHE AMCHEPIMUM</t>
+  </si>
+  <si>
+    <t>CHE EPADAHIVATUM</t>
+  </si>
+  <si>
+    <t>CHE ENATARAP</t>
+  </si>
+  <si>
+    <t>CHE MTATAP</t>
+  </si>
+  <si>
+    <t>CHE KIMDAMNATAM UNEJAMIAMU S</t>
+  </si>
+  <si>
+    <t>CHE KIMDAMNATAM UNEJAMIAMU SAS</t>
+  </si>
+  <si>
+    <t>CHE AMUIMTAPALAM</t>
+  </si>
+  <si>
+    <t>SHRIE RIMTANUM</t>
+  </si>
+  <si>
+    <t>CHE RANAHAKAPIUM</t>
+  </si>
+  <si>
+    <t>CHE UVIMD AVASAM</t>
+  </si>
+  <si>
+    <t>CHE BIMDAKUM</t>
+  </si>
+  <si>
+    <t>CHE CHAMPAP AIME</t>
+  </si>
+  <si>
+    <t>CHE KIMDAKIMTAM EJIPAJ MKUMKAMAMI</t>
+  </si>
+  <si>
+    <t>CHE HAMDAMEICHANAT</t>
+  </si>
+  <si>
+    <t>CHE EMIPADUMT</t>
+  </si>
+  <si>
+    <t>SHRIE CHAMTEM</t>
+  </si>
+  <si>
+    <t>SHRIE NAJATAMNASAM</t>
+  </si>
+  <si>
+    <t>SHRIE EPEUM INARANATAH</t>
+  </si>
+  <si>
+    <t>CHE CHAMKATAPALAM</t>
+  </si>
+  <si>
+    <t>CHE UVIMD AVASAP</t>
+  </si>
+  <si>
+    <t>CHE HAMKATAMAIM</t>
+  </si>
+  <si>
+    <t>CHE UMDAPAMNATAM</t>
+  </si>
+  <si>
+    <t>CHE AIMPATIMDAPALAM NAT IMDATAMIP</t>
+  </si>
+  <si>
+    <t>CHE IMPAKAMNASAP</t>
+  </si>
+  <si>
+    <t>CHE TAVAUMD KAMAP</t>
+  </si>
+  <si>
+    <t>CHE AIMPATAP NAT IRINADAHIMUM</t>
+  </si>
+  <si>
+    <t>CHE TMRAMAVIM NAT ICHTAMJAMCHACHANAT AIJBHPJ JAMNASAPIMUM</t>
+  </si>
+  <si>
+    <t>CHE PJAMIPALAM EJIPAJ TMRAMAVIM NAT ICHTAMJAMCHACHANAT</t>
+  </si>
+  <si>
+    <t>CHE KIMDAMNATAM AMEIP CHATAMEMK</t>
+  </si>
+  <si>
+    <t>SHRIE AIMPATAM</t>
+  </si>
+  <si>
+    <t>CHE IMEMIPALAM 2</t>
+  </si>
+  <si>
+    <t>CHE IMEMIPALAM S</t>
+  </si>
+  <si>
+    <t>CHE PAUSAPALAM SHR|CHAVVTHAP</t>
+  </si>
+  <si>
+    <t>BBHM BH|T|AIPDACH|J|D K|CH|PSHRADYATHABHSHRCHADYAK</t>
+  </si>
+  <si>
+    <t>CHE IMSAMNATAM</t>
+  </si>
+  <si>
+    <t>CHE BIMUCHAMCHANAT</t>
+  </si>
+  <si>
+    <t>CHE AIMKANAMAPALAM DAMDAMT</t>
+  </si>
+  <si>
+    <t>CHE DAPAIP EJIPAJ AVAUMT</t>
+  </si>
+  <si>
+    <t>CHE CHAMTEVIPALAM DAMDAMT</t>
+  </si>
+  <si>
+    <t>CHE THABHMK UNEJAMIAMU</t>
+  </si>
+  <si>
+    <t>CHE KAVIMTAPALAM AINATAK</t>
+  </si>
+  <si>
+    <t>CHE KAVIMTAPALAM INARANATAH</t>
+  </si>
+  <si>
+    <t>CHE EMAUTAM</t>
+  </si>
+  <si>
+    <t>SAMS IMIMKANAT IEE TAMUUMCHANAT JAPUMTAP</t>
+  </si>
+  <si>
+    <t>CHE IMHIMUM</t>
+  </si>
+  <si>
+    <t>CHE AINADANUM</t>
+  </si>
+  <si>
+    <t>CHE MJIAVADAPALAM</t>
+  </si>
+  <si>
+    <t>CHE HANARATAMNASAPALAM</t>
+  </si>
+  <si>
+    <t>CHE AMTAMIPALAM</t>
+  </si>
+  <si>
+    <t>CHE UMISAP</t>
+  </si>
+  <si>
+    <t>CHAMDABIMLAMJ IIMAMD UMKATAMIDAM RAMDANAIP</t>
+  </si>
+  <si>
+    <t>CHE UMISAM</t>
+  </si>
+  <si>
+    <t>CHE UMKATAMIDAM NAT ITAMU DAMHAMT</t>
+  </si>
+  <si>
+    <t>AIIMIMAMAK IIMHAMJ EPADAHI SHRIE IMRAMIM</t>
+  </si>
+  <si>
+    <t>CHE CHAMATAP NAT IUNATAPASAM</t>
+  </si>
+  <si>
+    <t>CHE IIMJAMNASAP</t>
+  </si>
+  <si>
+    <t>CHE MHALAM AINATAK</t>
+  </si>
+  <si>
+    <t>CHE RAMUNIMUM</t>
+  </si>
+  <si>
+    <t>CHE TAMUUMCHANAT JAVASAM UNEIMTUM S</t>
+  </si>
+  <si>
+    <t>CHE ENATALAMANAKAPALAM</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAJAM KAMAP</t>
+  </si>
+  <si>
+    <t>CHE EPAJAMTAMUCHANAT</t>
+  </si>
+  <si>
+    <t>CHE BIMAMP RAVAJ</t>
+  </si>
+  <si>
+    <t>CHE UMIKAMUM UPEITAM</t>
+  </si>
+  <si>
+    <t>CHE MIPATAMNASAP</t>
+  </si>
+  <si>
+    <t>CHE CHAMTEM UN MSAPAKAMCHANAT JAV IMIMKANATACHANAT</t>
+  </si>
+  <si>
+    <t>CHE CHMTEM</t>
+  </si>
+  <si>
+    <t>CHE MSAPAKAMCHANAT JAVASAM HAMNATAM IMRAMT</t>
+  </si>
+  <si>
+    <t>CHE UMTUMJAPALAM ANATAUP</t>
+  </si>
+  <si>
+    <t>CHE HAMLAHIMJ</t>
+  </si>
+  <si>
+    <t>CHE IIMKAMIMT HATAMDAJ</t>
+  </si>
+  <si>
+    <t>CHE AMCHAPALAM INADAPIM HATAMDAJ</t>
+  </si>
+  <si>
+    <t>CHE AMCHAPALAM HATAMDAJ</t>
+  </si>
+  <si>
+    <t>CHAMDABIMLAMJ IIMUMD AMCHAPALAM AIMSEM</t>
+  </si>
+  <si>
+    <t>CHE IMTAHAV</t>
+  </si>
+  <si>
+    <t>CHE TAMOIM</t>
+  </si>
+  <si>
+    <t>PANCHAYAT BHAWAN KARAUTI</t>
+  </si>
+  <si>
+    <t>CHE SANABINAMAPALAM</t>
+  </si>
+  <si>
+    <t>CHE KANAIMNASAPALAM</t>
+  </si>
+  <si>
+    <t>SHRIE IMASUM</t>
+  </si>
+  <si>
+    <t>CHE UMIKAMUM</t>
+  </si>
+  <si>
+    <t>SHRATHABHDYAJBH|THABHK|K THATHABHKL|AIBHTBBH|KL|J~NADY|PKL|AIBHT|KL|J~NADYASHRAKL|JBH|THABHKL|J~NADYASHRCH|KL|SHR SKL|J~NADYASHRCH|KL|AIBHTBBH|KL|J~NADYABBH|J~NADYASHRCH|SHRCH|JBH|THABH</t>
+  </si>
+  <si>
+    <t>CHE EMADAKANATAP</t>
+  </si>
+  <si>
+    <t>SHRATHABHDYABBHJ~NADYASHRCH|KL|AIBHTBBH|KL|AIBHT KL|BBHSHRATHABHDYAJBH|THABHJ~NADY|PTHABHJTHATHABHKL|SHRATHABHDYAJBH|THABHJ~NASDYAIBHT J~NADYASHRAKL|J~NADYAIBHTBBH DYACHJBH|THABHSHRABBHK BBH|THATHABHKL|AIBHT|KL|THATHABHKLDYACHKL|J~N BBHTHATHABHKL|SHRAKL|THATHABHKL|AIBHT|KL|JBH|THABH</t>
+  </si>
+  <si>
+    <t>CHE BIPASIPALAM</t>
+  </si>
+  <si>
+    <t>CHE HANARATAMNASAPALAM HATAMDAJ</t>
+  </si>
+  <si>
+    <t>CHE AMNAM</t>
+  </si>
+  <si>
+    <t>CHE UNATAPASAM AINATAK</t>
+  </si>
+  <si>
+    <t>CHE JAMADAMT</t>
+  </si>
+  <si>
+    <t>CHE UMKATAMIDAM NAT IKAMJAJACHANAT</t>
+  </si>
+  <si>
+    <t>CHE BIVATAMT</t>
+  </si>
+  <si>
+    <t>CHE DAPALAM</t>
+  </si>
+  <si>
+    <t>PANCHAYAT BHAWAN BHADAV</t>
+  </si>
+  <si>
+    <t>CHE BIMAJATAM S</t>
+  </si>
+  <si>
+    <t>CHE BIMAJATAM SAS</t>
+  </si>
+  <si>
+    <t>CHE AMTAUM</t>
+  </si>
+  <si>
+    <t>CHE DAMKAMNATAM</t>
+  </si>
+  <si>
+    <t>CHE IMIIDAP</t>
+  </si>
+  <si>
+    <t>CHE EPALAM DAMDAMT</t>
+  </si>
+  <si>
+    <t>SHRIE TAMUUMCHANAT DAMDAMT</t>
+  </si>
+  <si>
+    <t>SHRIE UMIKAMUM DAMDAMT</t>
+  </si>
+  <si>
+    <t>CHE UMATAMNAT</t>
+  </si>
+  <si>
+    <t>CHE IMHANASAMIUM</t>
+  </si>
+  <si>
+    <t>CHE UMIJIM</t>
+  </si>
+  <si>
+    <t>SHRIE UMSAHAMUM</t>
+  </si>
+  <si>
+    <t>CHE UMKUM</t>
+  </si>
+  <si>
+    <t>CHE HAMRIMKAM</t>
+  </si>
+  <si>
+    <t>CHE SAMAKUM UMPI</t>
+  </si>
+  <si>
+    <t>CHE CHAMTAPAHAMUM</t>
+  </si>
+  <si>
+    <t>CHE DAMAJIMT</t>
+  </si>
+  <si>
+    <t>CHE AVAPATAP KAMAMI</t>
+  </si>
+  <si>
+    <t>CHE BIMJAMIMTAP</t>
+  </si>
+  <si>
+    <t>AMDALAM SHRIE EIVITAMJAHAMTI EJIPAJ DAPAIP</t>
+  </si>
+  <si>
+    <t>SHRIE EIVITAMJAHAMTI EJIPAJ HAMTAMANAS</t>
+  </si>
+  <si>
+    <t>CHE BIMJIMTAM</t>
+  </si>
+  <si>
+    <t>AIIPAMCHAMJAP PDAJAMAT BVASASAMAHAM AIIVITAMJAHAMTI BAVAUMATABAPAMS INASAKAPADAH</t>
+  </si>
+  <si>
+    <t>UMTUMKAP KIMTAUEIMSAM EIVITAMJAHAMTI</t>
+  </si>
+  <si>
+    <t>CHE CHAMTEPALAM</t>
+  </si>
+  <si>
+    <t>CHE KAMIPALAMK</t>
+  </si>
+  <si>
+    <t>CHE CHAMATAP</t>
+  </si>
+  <si>
+    <t>CHE INAKIMCHAMT</t>
+  </si>
+  <si>
+    <t>CHE UMIDAMNASAP</t>
+  </si>
+  <si>
+    <t>CHE MHALAM</t>
+  </si>
+  <si>
+    <t>CHE BIMNIMJAJAM</t>
+  </si>
+  <si>
+    <t>CHE AIMTAMHUMT</t>
+  </si>
+  <si>
+    <t>CHE KAMTIM DAMDAMT</t>
+  </si>
+  <si>
+    <t>SHRIE UMIUNAKUM HATAMDAJ</t>
+  </si>
+  <si>
+    <t>CHE MJATAP</t>
+  </si>
+  <si>
+    <t>CHE TAMUMCHANAT</t>
+  </si>
+  <si>
+    <t>SHRIE DAMKUMSAPALAM</t>
+  </si>
+  <si>
+    <t>CHE AVAJAPALAM KAPAHAMT</t>
+  </si>
+  <si>
+    <t>CHE IMASAIIMTAPALAM</t>
+  </si>
+  <si>
+    <t>CHE RAMAIMNASAPALAM</t>
+  </si>
+  <si>
+    <t>CHE EPATEPALAM UPEITAM</t>
+  </si>
+  <si>
+    <t>CHE KIMDAHAMKIPALAM</t>
+  </si>
+  <si>
+    <t>CHE MATAM</t>
+  </si>
+  <si>
+    <t>CHE RAMUIPATAPALAM</t>
+  </si>
+  <si>
+    <t>CHE IMPARADAMJIM</t>
+  </si>
+  <si>
+    <t>CHE EPATEPALAM TAMRAM</t>
+  </si>
+  <si>
+    <t>CHE IMTAMPADAPALAM</t>
+  </si>
+  <si>
+    <t>CHE DAMAMIP</t>
+  </si>
+  <si>
+    <t>CHE IIMCHEP</t>
+  </si>
+  <si>
+    <t>CHE CHAMTEVIPALAM</t>
+  </si>
+  <si>
+    <t>CHE BIMCHAPALAM HAMHUM</t>
+  </si>
+  <si>
+    <t>CHE AIMAJUMS UPEITAM</t>
+  </si>
+  <si>
+    <t>CHE KAMITAM</t>
+  </si>
+  <si>
+    <t>CHE ANASAHAMUMCHANAT</t>
+  </si>
+  <si>
+    <t>CHE DAMHACHATAM S</t>
+  </si>
+  <si>
+    <t>CHE DAMHACHATAM SAS</t>
+  </si>
+  <si>
+    <t>CHE CHAPACHATAMIUM</t>
+  </si>
+  <si>
+    <t>SHRIE UMRIUMD</t>
+  </si>
+  <si>
+    <t>CHE EIMIM</t>
+  </si>
+  <si>
+    <t>CHE SAMAIMDACHAMTAM</t>
+  </si>
+  <si>
+    <t>CHE EMINAMAP</t>
+  </si>
+  <si>
+    <t>CHE RANATAPANAMAPALAM</t>
+  </si>
+  <si>
+    <t>CHE AVAMAPASAPAHIMJ</t>
+  </si>
+  <si>
+    <t>CHE JAMKAPALAM</t>
+  </si>
+  <si>
+    <t>CHE RAVAHAPAIMTAP</t>
+  </si>
+  <si>
+    <t>CHE UMERAPAKAPALAM EJIPAJ CHAPACHATAP S</t>
+  </si>
+  <si>
+    <t>CHE UMERAPAKAPALAM EJIPAJ CHAPACHATAP SAS</t>
+  </si>
+  <si>
+    <t>CHE MAKAMAHAMUM IIMACHANAT HATAMDAJ</t>
+  </si>
+  <si>
+    <t>CHE IMASAHAMKAM</t>
+  </si>
+  <si>
+    <t>CHE RAMHAMTAHAMJIPALAM</t>
+  </si>
+  <si>
+    <t>CHE EMDAJAVATAM</t>
+  </si>
+  <si>
+    <t>CHE RAMUNADAP</t>
+  </si>
+  <si>
+    <t>CHE UMIKAMUM HAMDAHAMTAMU</t>
+  </si>
+  <si>
+    <t>CHE AMJALAM</t>
+  </si>
+  <si>
+    <t>CHE AMDANUMKAMAMI</t>
+  </si>
+  <si>
+    <t>CHE CHAMTAMECHAPADAKAM</t>
+  </si>
+  <si>
+    <t>CHE EMINAKAM</t>
+  </si>
+  <si>
+    <t>CHE BIMDAMTAHAMKAKAP</t>
+  </si>
+  <si>
+    <t>MDAHAMDUMKAP AMADAKATAM AMTAMNAKAM DAMDAMT</t>
+  </si>
+  <si>
+    <t>SHRIE IMTAHAMKUM</t>
+  </si>
+  <si>
+    <t>CHE IMEJIM</t>
+  </si>
+  <si>
+    <t>CHE KINENATAP INARANATAH</t>
+  </si>
+  <si>
+    <t>CHE EMAUTAPALAM DAMDAMT</t>
+  </si>
+  <si>
+    <t>CHE EPATUMJ</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM NO. 362</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM NO. 363</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM NO. 364</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM NO. 365</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM NO. 366</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM NO. 367</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 368</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 369</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 370</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 371</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 372</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 373</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 374</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 375</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 376</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 377</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 378</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 379</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 380</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 381</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 382</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 383</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 384</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 385</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 386</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 387</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 388</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 389</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 390</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 391</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 392</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 393</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 394</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 395</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 396</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 397</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 398</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 399</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 400</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 401</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 402</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 403</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 404</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 405</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 406</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 407</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 408</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 409</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 410</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 411</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 412</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 413</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 414</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 415</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 416</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 417</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 418</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 419</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 420</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 421</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 422</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 423</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 424</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 425</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 426</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 427</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 428</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 429</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 430</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 431</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 432</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 433</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 434</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 435</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 436</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 437</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 438</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 439</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 440</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 441</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 442</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 443</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 444</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 445</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 446</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 447</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 448</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 449</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 450</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 451</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 452</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 453</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 454</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 455</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 456</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 457</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 458</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 459</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 460</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 461</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 462</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 463</t>
+  </si>
+  <si>
+    <t>CHE CHAMSAPALAM JAMAKIMT ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 464</t>
   </si>
   <si>
     <t>TOTAL ELECTORS</t>
@@ -473,8 +1343,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -490,7 +1368,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -498,12 +1376,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -802,88 +1698,163 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:26">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>418</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>419</v>
       </c>
       <c r="E2" t="s">
-        <v>130</v>
+        <v>420</v>
       </c>
       <c r="F2" t="s">
-        <v>131</v>
+        <v>421</v>
       </c>
       <c r="G2" t="s">
-        <v>132</v>
+        <v>422</v>
       </c>
       <c r="H2" t="s">
-        <v>133</v>
+        <v>423</v>
       </c>
       <c r="I2" t="s">
-        <v>134</v>
+        <v>424</v>
       </c>
       <c r="J2" t="s">
-        <v>135</v>
+        <v>425</v>
       </c>
       <c r="K2" t="s">
-        <v>136</v>
+        <v>426</v>
       </c>
       <c r="L2" t="s">
-        <v>137</v>
+        <v>427</v>
       </c>
       <c r="M2" t="s">
-        <v>138</v>
+        <v>428</v>
       </c>
       <c r="N2" t="s">
-        <v>139</v>
+        <v>429</v>
       </c>
       <c r="O2" t="s">
-        <v>140</v>
+        <v>430</v>
       </c>
       <c r="P2" t="s">
-        <v>141</v>
+        <v>431</v>
       </c>
       <c r="Q2" t="s">
-        <v>142</v>
+        <v>432</v>
       </c>
       <c r="R2" t="s">
-        <v>143</v>
+        <v>433</v>
       </c>
       <c r="S2" t="s">
-        <v>144</v>
+        <v>434</v>
       </c>
       <c r="T2" t="s">
-        <v>145</v>
+        <v>435</v>
       </c>
       <c r="U2" t="s">
-        <v>146</v>
+        <v>436</v>
       </c>
       <c r="V2" t="s">
-        <v>147</v>
+        <v>437</v>
       </c>
       <c r="W2" t="s">
-        <v>148</v>
+        <v>438</v>
       </c>
       <c r="X2" t="s">
-        <v>148</v>
+        <v>438</v>
       </c>
       <c r="Y2" t="s">
-        <v>149</v>
+        <v>439</v>
       </c>
       <c r="Z2" t="s">
-        <v>150</v>
+        <v>440</v>
       </c>
     </row>
     <row r="3" spans="1:26">
@@ -891,7 +1862,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C3">
         <v>1085</v>
@@ -971,7 +1942,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C4">
         <v>716</v>
@@ -1051,7 +2022,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="C5">
         <v>942</v>
@@ -1131,7 +2102,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="C6">
         <v>760</v>
@@ -1211,7 +2182,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="C7">
         <v>501</v>
@@ -1291,7 +2262,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="C8">
         <v>0</v>
@@ -1371,7 +2342,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="C9">
         <v>700</v>
@@ -1451,7 +2422,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="C10">
         <v>902</v>
@@ -1531,7 +2502,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="C11">
         <v>581</v>
@@ -1611,7 +2582,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="C12">
         <v>659</v>
@@ -1691,7 +2662,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="C13">
         <v>1045</v>
@@ -1771,7 +2742,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="C14">
         <v>709</v>
@@ -1851,7 +2822,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="C15">
         <v>524</v>
@@ -1931,7 +2902,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>13</v>
+        <v>41</v>
       </c>
       <c r="C16">
         <v>634</v>
@@ -2011,7 +2982,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="C17">
         <v>621</v>
@@ -2091,7 +3062,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>12</v>
+        <v>43</v>
       </c>
       <c r="C18">
         <v>501</v>
@@ -2171,7 +3142,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="C19">
         <v>606</v>
@@ -2251,7 +3222,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="C20">
         <v>581</v>
@@ -2331,7 +3302,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="C21">
         <v>406</v>
@@ -2411,7 +3382,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="C22">
         <v>621</v>
@@ -2491,7 +3462,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="C23">
         <v>644</v>
@@ -2571,7 +3542,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="C24">
         <v>839</v>
@@ -2651,7 +3622,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="C25">
         <v>698</v>
@@ -2731,7 +3702,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="C26">
         <v>527</v>
@@ -2811,7 +3782,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="C27">
         <v>674</v>
@@ -2891,7 +3862,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="C28">
         <v>643</v>
@@ -2971,7 +3942,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>18</v>
+        <v>52</v>
       </c>
       <c r="C29">
         <v>940</v>
@@ -3051,7 +4022,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="C30">
         <v>695</v>
@@ -3131,7 +4102,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="C31">
         <v>893</v>
@@ -3211,7 +4182,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="C32">
         <v>864</v>
@@ -3291,7 +4262,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="C33">
         <v>705</v>
@@ -3371,7 +4342,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="C34">
         <v>553</v>
@@ -3451,7 +4422,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="C35">
         <v>679</v>
@@ -3531,7 +4502,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="C36">
         <v>859</v>
@@ -3611,7 +4582,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="C37">
         <v>864</v>
@@ -3691,7 +4662,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="C38">
         <v>931</v>
@@ -3771,7 +4742,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="C39">
         <v>560</v>
@@ -3851,7 +4822,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>21</v>
+        <v>63</v>
       </c>
       <c r="C40">
         <v>1188</v>
@@ -3931,7 +4902,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="C41">
         <v>675</v>
@@ -4011,7 +4982,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>11</v>
+        <v>65</v>
       </c>
       <c r="C42">
         <v>938</v>
@@ -4091,7 +5062,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="C43">
         <v>859</v>
@@ -4171,7 +5142,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="C44">
         <v>720</v>
@@ -4251,7 +5222,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>23</v>
+        <v>68</v>
       </c>
       <c r="C45">
         <v>522</v>
@@ -4331,7 +5302,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>23</v>
+        <v>69</v>
       </c>
       <c r="C46">
         <v>648</v>
@@ -4411,7 +5382,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="C47">
         <v>611</v>
@@ -4491,7 +5462,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>16</v>
+        <v>70</v>
       </c>
       <c r="C48">
         <v>649</v>
@@ -4571,7 +5542,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>16</v>
+        <v>71</v>
       </c>
       <c r="C49">
         <v>673</v>
@@ -4651,7 +5622,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="C50">
         <v>946</v>
@@ -4731,7 +5702,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="C51">
         <v>484</v>
@@ -4811,7 +5782,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>16</v>
+        <v>73</v>
       </c>
       <c r="C52">
         <v>624</v>
@@ -4891,7 +5862,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="C53">
         <v>899</v>
@@ -4971,7 +5942,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="C54">
         <v>772</v>
@@ -5051,7 +6022,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>11</v>
+        <v>76</v>
       </c>
       <c r="C55">
         <v>598</v>
@@ -5131,7 +6102,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="C56">
         <v>523</v>
@@ -5211,7 +6182,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="C57">
         <v>897</v>
@@ -5291,7 +6262,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="C58">
         <v>861</v>
@@ -5371,7 +6342,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="C59">
         <v>679</v>
@@ -5451,7 +6422,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="C60">
         <v>879</v>
@@ -5531,7 +6502,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="C61">
         <v>804</v>
@@ -5611,7 +6582,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="C62">
         <v>622</v>
@@ -5691,7 +6662,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="C63">
         <v>915</v>
@@ -5771,7 +6742,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>27</v>
+        <v>82</v>
       </c>
       <c r="C64">
         <v>726</v>
@@ -5851,7 +6822,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="C65">
         <v>625</v>
@@ -5931,7 +6902,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="C66">
         <v>540</v>
@@ -6011,7 +6982,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="C67">
         <v>673</v>
@@ -6091,7 +7062,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>27</v>
+        <v>85</v>
       </c>
       <c r="C68">
         <v>593</v>
@@ -6171,7 +7142,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="C69">
         <v>635</v>
@@ -6251,7 +7222,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="C70">
         <v>710</v>
@@ -6331,7 +7302,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>27</v>
+        <v>86</v>
       </c>
       <c r="C71">
         <v>711</v>
@@ -6411,7 +7382,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>28</v>
+        <v>86</v>
       </c>
       <c r="C72">
         <v>1093</v>
@@ -6491,7 +7462,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="C73">
         <v>1028</v>
@@ -6571,7 +7542,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>30</v>
+        <v>87</v>
       </c>
       <c r="C74">
         <v>850</v>
@@ -6651,7 +7622,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>31</v>
+        <v>88</v>
       </c>
       <c r="C75">
         <v>587</v>
@@ -6731,7 +7702,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>16</v>
+        <v>88</v>
       </c>
       <c r="C76">
         <v>612</v>
@@ -6811,7 +7782,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>32</v>
+        <v>89</v>
       </c>
       <c r="C77">
         <v>963</v>
@@ -6891,7 +7862,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>33</v>
+        <v>89</v>
       </c>
       <c r="C78">
         <v>796</v>
@@ -6971,7 +7942,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>29</v>
+        <v>90</v>
       </c>
       <c r="C79">
         <v>796</v>
@@ -7051,7 +8022,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="C80">
         <v>735</v>
@@ -7131,7 +8102,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>34</v>
+        <v>92</v>
       </c>
       <c r="C81">
         <v>746</v>
@@ -7211,7 +8182,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>34</v>
+        <v>93</v>
       </c>
       <c r="C82">
         <v>955</v>
@@ -7291,7 +8262,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="C83">
         <v>598</v>
@@ -7371,7 +8342,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="C84">
         <v>836</v>
@@ -7451,7 +8422,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>34</v>
+        <v>96</v>
       </c>
       <c r="C85">
         <v>823</v>
@@ -7531,7 +8502,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>10</v>
+        <v>97</v>
       </c>
       <c r="C86">
         <v>559</v>
@@ -7611,7 +8582,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>10</v>
+        <v>98</v>
       </c>
       <c r="C87">
         <v>633</v>
@@ -7691,7 +8662,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>11</v>
+        <v>98</v>
       </c>
       <c r="C88">
         <v>653</v>
@@ -7771,7 +8742,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>11</v>
+        <v>99</v>
       </c>
       <c r="C89">
         <v>729</v>
@@ -7851,7 +8822,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>35</v>
+        <v>100</v>
       </c>
       <c r="C90">
         <v>696</v>
@@ -7931,7 +8902,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="C91">
         <v>639</v>
@@ -8011,7 +8982,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="C92">
         <v>724</v>
@@ -8091,7 +9062,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>36</v>
+        <v>103</v>
       </c>
       <c r="C93">
         <v>683</v>
@@ -8171,7 +9142,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>37</v>
+        <v>104</v>
       </c>
       <c r="C94">
         <v>723</v>
@@ -8251,7 +9222,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>37</v>
+        <v>105</v>
       </c>
       <c r="C95">
         <v>618</v>
@@ -8331,7 +9302,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>30</v>
+        <v>106</v>
       </c>
       <c r="C96">
         <v>687</v>
@@ -8411,7 +9382,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
       <c r="C97">
         <v>686</v>
@@ -8491,7 +9462,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>24</v>
+        <v>107</v>
       </c>
       <c r="C98">
         <v>0</v>
@@ -8571,7 +9542,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>24</v>
+        <v>108</v>
       </c>
       <c r="C99">
         <v>517</v>
@@ -8651,7 +9622,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C100">
         <v>975</v>
@@ -8731,7 +9702,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>24</v>
+        <v>109</v>
       </c>
       <c r="C101">
         <v>845</v>
@@ -8811,7 +9782,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>30</v>
+        <v>109</v>
       </c>
       <c r="C102">
         <v>981</v>
@@ -8891,7 +9862,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>38</v>
+        <v>109</v>
       </c>
       <c r="C103">
         <v>672</v>
@@ -8971,7 +9942,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>38</v>
+        <v>109</v>
       </c>
       <c r="C104">
         <v>670</v>
@@ -9051,7 +10022,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>30</v>
+        <v>109</v>
       </c>
       <c r="C105">
         <v>996</v>
@@ -9131,7 +10102,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>39</v>
+        <v>110</v>
       </c>
       <c r="C106">
         <v>691</v>
@@ -9211,7 +10182,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>39</v>
+        <v>110</v>
       </c>
       <c r="C107">
         <v>645</v>
@@ -9291,7 +10262,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>33</v>
+        <v>110</v>
       </c>
       <c r="C108">
         <v>846</v>
@@ -9371,7 +10342,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>33</v>
+        <v>110</v>
       </c>
       <c r="C109">
         <v>1043</v>
@@ -9451,7 +10422,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>9</v>
+        <v>110</v>
       </c>
       <c r="C110">
         <v>575</v>
@@ -9531,7 +10502,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>11</v>
+        <v>110</v>
       </c>
       <c r="C111">
         <v>651</v>
@@ -9611,7 +10582,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>16</v>
+        <v>111</v>
       </c>
       <c r="C112">
         <v>677</v>
@@ -9691,7 +10662,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>40</v>
+        <v>112</v>
       </c>
       <c r="C113">
         <v>795</v>
@@ -9771,7 +10742,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>40</v>
+        <v>113</v>
       </c>
       <c r="C114">
         <v>807</v>
@@ -9851,7 +10822,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>41</v>
+        <v>114</v>
       </c>
       <c r="C115">
         <v>873</v>
@@ -9931,7 +10902,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>41</v>
+        <v>115</v>
       </c>
       <c r="C116">
         <v>447</v>
@@ -10011,7 +10982,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>10</v>
+        <v>116</v>
       </c>
       <c r="C117">
         <v>1130</v>
@@ -10091,7 +11062,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>10</v>
+        <v>117</v>
       </c>
       <c r="C118">
         <v>677</v>
@@ -10171,7 +11142,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>10</v>
+        <v>118</v>
       </c>
       <c r="C119">
         <v>875</v>
@@ -10251,7 +11222,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>11</v>
+        <v>119</v>
       </c>
       <c r="C120">
         <v>834</v>
@@ -10331,7 +11302,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>34</v>
+        <v>120</v>
       </c>
       <c r="C121">
         <v>667</v>
@@ -10411,7 +11382,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>42</v>
+        <v>121</v>
       </c>
       <c r="C122">
         <v>625</v>
@@ -10491,7 +11462,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>42</v>
+        <v>121</v>
       </c>
       <c r="C123">
         <v>738</v>
@@ -10571,7 +11542,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>9</v>
+        <v>122</v>
       </c>
       <c r="C124">
         <v>705</v>
@@ -10651,7 +11622,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>43</v>
+        <v>123</v>
       </c>
       <c r="C125">
         <v>938</v>
@@ -10731,7 +11702,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>44</v>
+        <v>124</v>
       </c>
       <c r="C126">
         <v>436</v>
@@ -10811,7 +11782,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>45</v>
+        <v>125</v>
       </c>
       <c r="C127">
         <v>0</v>
@@ -10891,7 +11862,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>30</v>
+        <v>126</v>
       </c>
       <c r="C128">
         <v>786</v>
@@ -10971,7 +11942,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>10</v>
+        <v>127</v>
       </c>
       <c r="C129">
         <v>321</v>
@@ -11051,7 +12022,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="C130">
         <v>737</v>
@@ -11131,7 +12102,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>33</v>
+        <v>129</v>
       </c>
       <c r="C131">
         <v>705</v>
@@ -11211,7 +12182,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>33</v>
+        <v>130</v>
       </c>
       <c r="C132">
         <v>620</v>
@@ -11291,7 +12262,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>46</v>
+        <v>131</v>
       </c>
       <c r="C133">
         <v>604</v>
@@ -11371,7 +12342,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>11</v>
+        <v>132</v>
       </c>
       <c r="C134">
         <v>883</v>
@@ -11451,7 +12422,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>9</v>
+        <v>133</v>
       </c>
       <c r="C135">
         <v>976</v>
@@ -11531,7 +12502,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>9</v>
+        <v>134</v>
       </c>
       <c r="C136">
         <v>1028</v>
@@ -11611,7 +12582,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>47</v>
+        <v>135</v>
       </c>
       <c r="C137">
         <v>1021</v>
@@ -11691,7 +12662,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>47</v>
+        <v>136</v>
       </c>
       <c r="C138">
         <v>878</v>
@@ -11771,7 +12742,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
       <c r="C139">
         <v>717</v>
@@ -11851,7 +12822,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>48</v>
+        <v>137</v>
       </c>
       <c r="C140">
         <v>722</v>
@@ -11931,7 +12902,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>49</v>
+        <v>138</v>
       </c>
       <c r="C141">
         <v>388</v>
@@ -12011,7 +12982,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>50</v>
+        <v>139</v>
       </c>
       <c r="C142">
         <v>752</v>
@@ -12091,7 +13062,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>41</v>
+        <v>140</v>
       </c>
       <c r="C143">
         <v>896</v>
@@ -12171,7 +13142,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>13</v>
+        <v>141</v>
       </c>
       <c r="C144">
         <v>766</v>
@@ -12251,7 +13222,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>13</v>
+        <v>142</v>
       </c>
       <c r="C145">
         <v>760</v>
@@ -12331,7 +13302,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>11</v>
+        <v>143</v>
       </c>
       <c r="C146">
         <v>645</v>
@@ -12411,7 +13382,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>11</v>
+        <v>144</v>
       </c>
       <c r="C147">
         <v>609</v>
@@ -12491,7 +13462,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>12</v>
+        <v>145</v>
       </c>
       <c r="C148">
         <v>683</v>
@@ -12571,7 +13542,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>51</v>
+        <v>146</v>
       </c>
       <c r="C149">
         <v>935</v>
@@ -12651,7 +13622,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>51</v>
+        <v>147</v>
       </c>
       <c r="C150">
         <v>511</v>
@@ -12731,7 +13702,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>16</v>
+        <v>148</v>
       </c>
       <c r="C151">
         <v>551</v>
@@ -12811,7 +13782,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>10</v>
+        <v>149</v>
       </c>
       <c r="C152">
         <v>1068</v>
@@ -12891,7 +13862,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="C153">
         <v>325</v>
@@ -12971,7 +13942,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>52</v>
+        <v>151</v>
       </c>
       <c r="C154">
         <v>740</v>
@@ -13051,7 +14022,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>52</v>
+        <v>152</v>
       </c>
       <c r="C155">
         <v>643</v>
@@ -13131,7 +14102,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>53</v>
+        <v>153</v>
       </c>
       <c r="C156">
         <v>678</v>
@@ -13211,7 +14182,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>54</v>
+        <v>154</v>
       </c>
       <c r="C157">
         <v>939</v>
@@ -13291,7 +14262,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>34</v>
+        <v>155</v>
       </c>
       <c r="C158">
         <v>1016</v>
@@ -13371,7 +14342,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>55</v>
+        <v>156</v>
       </c>
       <c r="C159">
         <v>1036</v>
@@ -13451,7 +14422,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>55</v>
+        <v>157</v>
       </c>
       <c r="C160">
         <v>754</v>
@@ -13531,7 +14502,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>56</v>
+        <v>158</v>
       </c>
       <c r="C161">
         <v>910</v>
@@ -13611,7 +14582,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>56</v>
+        <v>159</v>
       </c>
       <c r="C162">
         <v>426</v>
@@ -13691,7 +14662,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>57</v>
+        <v>160</v>
       </c>
       <c r="C163">
         <v>912</v>
@@ -13771,7 +14742,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>16</v>
+        <v>161</v>
       </c>
       <c r="C164">
         <v>693</v>
@@ -13851,7 +14822,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>58</v>
+        <v>161</v>
       </c>
       <c r="C165">
         <v>718</v>
@@ -13931,7 +14902,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>58</v>
+        <v>162</v>
       </c>
       <c r="C166">
         <v>766</v>
@@ -14011,7 +14982,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>24</v>
+        <v>162</v>
       </c>
       <c r="C167">
         <v>752</v>
@@ -14091,7 +15062,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>30</v>
+        <v>163</v>
       </c>
       <c r="C168">
         <v>654</v>
@@ -14171,7 +15142,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>30</v>
+        <v>164</v>
       </c>
       <c r="C169">
         <v>603</v>
@@ -14251,7 +15222,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>37</v>
+        <v>165</v>
       </c>
       <c r="C170">
         <v>895</v>
@@ -14331,7 +15302,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>17</v>
+        <v>166</v>
       </c>
       <c r="C171">
         <v>810</v>
@@ -14411,7 +15382,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>11</v>
+        <v>167</v>
       </c>
       <c r="C172">
         <v>1000</v>
@@ -14491,7 +15462,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>34</v>
+        <v>167</v>
       </c>
       <c r="C173">
         <v>686</v>
@@ -14571,7 +15542,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>34</v>
+        <v>168</v>
       </c>
       <c r="C174">
         <v>541</v>
@@ -14651,7 +15622,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>59</v>
+        <v>169</v>
       </c>
       <c r="C175">
         <v>951</v>
@@ -14731,7 +15702,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>31</v>
+        <v>170</v>
       </c>
       <c r="C176">
         <v>666</v>
@@ -14811,7 +15782,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>60</v>
+        <v>171</v>
       </c>
       <c r="C177">
         <v>736</v>
@@ -14891,7 +15862,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>61</v>
+        <v>172</v>
       </c>
       <c r="C178">
         <v>879</v>
@@ -14971,7 +15942,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>61</v>
+        <v>173</v>
       </c>
       <c r="C179">
         <v>612</v>
@@ -15051,7 +16022,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>61</v>
+        <v>174</v>
       </c>
       <c r="C180">
         <v>996</v>
@@ -15131,7 +16102,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>62</v>
+        <v>175</v>
       </c>
       <c r="C181">
         <v>781</v>
@@ -15211,7 +16182,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>16</v>
+        <v>174</v>
       </c>
       <c r="C182">
         <v>837</v>
@@ -15291,7 +16262,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>63</v>
+        <v>176</v>
       </c>
       <c r="C183">
         <v>1093</v>
@@ -15371,7 +16342,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>30</v>
+        <v>177</v>
       </c>
       <c r="C184">
         <v>1101</v>
@@ -15451,7 +16422,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>30</v>
+        <v>178</v>
       </c>
       <c r="C185">
         <v>750</v>
@@ -15531,7 +16502,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>30</v>
+        <v>179</v>
       </c>
       <c r="C186">
         <v>551</v>
@@ -15611,7 +16582,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>64</v>
+        <v>180</v>
       </c>
       <c r="C187">
         <v>1023</v>
@@ -15691,7 +16662,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>64</v>
+        <v>181</v>
       </c>
       <c r="C188">
         <v>1017</v>
@@ -15771,7 +16742,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>64</v>
+        <v>182</v>
       </c>
       <c r="C189">
         <v>1012</v>
@@ -15851,7 +16822,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>65</v>
+        <v>183</v>
       </c>
       <c r="C190">
         <v>1000</v>
@@ -15931,7 +16902,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>65</v>
+        <v>184</v>
       </c>
       <c r="C191">
         <v>1059</v>
@@ -16011,7 +16982,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>38</v>
+        <v>185</v>
       </c>
       <c r="C192">
         <v>1104</v>
@@ -16091,7 +17062,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>38</v>
+        <v>186</v>
       </c>
       <c r="C193">
         <v>1136</v>
@@ -16171,7 +17142,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>44</v>
+        <v>187</v>
       </c>
       <c r="C194">
         <v>689</v>
@@ -16251,7 +17222,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>44</v>
+        <v>188</v>
       </c>
       <c r="C195">
         <v>679</v>
@@ -16331,7 +17302,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>66</v>
+        <v>189</v>
       </c>
       <c r="C196">
         <v>693</v>
@@ -16411,7 +17382,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>66</v>
+        <v>190</v>
       </c>
       <c r="C197">
         <v>614</v>
@@ -16491,7 +17462,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>67</v>
+        <v>190</v>
       </c>
       <c r="C198">
         <v>932</v>
@@ -16571,7 +17542,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>67</v>
+        <v>191</v>
       </c>
       <c r="C199">
         <v>810</v>
@@ -16651,7 +17622,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>67</v>
+        <v>192</v>
       </c>
       <c r="C200">
         <v>809</v>
@@ -16731,7 +17702,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>33</v>
+        <v>193</v>
       </c>
       <c r="C201">
         <v>460</v>
@@ -16811,7 +17782,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>68</v>
+        <v>194</v>
       </c>
       <c r="C202">
         <v>771</v>
@@ -16891,7 +17862,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>68</v>
+        <v>194</v>
       </c>
       <c r="C203">
         <v>712</v>
@@ -16971,7 +17942,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>31</v>
+        <v>195</v>
       </c>
       <c r="C204">
         <v>1041</v>
@@ -17051,7 +18022,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>31</v>
+        <v>195</v>
       </c>
       <c r="C205">
         <v>873</v>
@@ -17131,7 +18102,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>69</v>
+        <v>196</v>
       </c>
       <c r="C206">
         <v>941</v>
@@ -17211,7 +18182,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>69</v>
+        <v>196</v>
       </c>
       <c r="C207">
         <v>928</v>
@@ -17291,7 +18262,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>69</v>
+        <v>197</v>
       </c>
       <c r="C208">
         <v>920</v>
@@ -17371,7 +18342,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>70</v>
+        <v>197</v>
       </c>
       <c r="C209">
         <v>477</v>
@@ -17451,7 +18422,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>71</v>
+        <v>198</v>
       </c>
       <c r="C210">
         <v>925</v>
@@ -17531,7 +18502,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>71</v>
+        <v>198</v>
       </c>
       <c r="C211">
         <v>620</v>
@@ -17611,7 +18582,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>72</v>
+        <v>199</v>
       </c>
       <c r="C212">
         <v>611</v>
@@ -17691,7 +18662,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>72</v>
+        <v>199</v>
       </c>
       <c r="C213">
         <v>554</v>
@@ -17771,7 +18742,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>73</v>
+        <v>200</v>
       </c>
       <c r="C214">
         <v>595</v>
@@ -17851,7 +18822,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>33</v>
+        <v>201</v>
       </c>
       <c r="C215">
         <v>702</v>
@@ -17931,7 +18902,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>33</v>
+        <v>202</v>
       </c>
       <c r="C216">
         <v>0</v>
@@ -18011,7 +18982,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="C217">
         <v>644</v>
@@ -18091,7 +19062,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>31</v>
+        <v>203</v>
       </c>
       <c r="C218">
         <v>684</v>
@@ -18171,7 +19142,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>31</v>
+        <v>204</v>
       </c>
       <c r="C219">
         <v>728</v>
@@ -18251,7 +19222,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>24</v>
+        <v>204</v>
       </c>
       <c r="C220">
         <v>830</v>
@@ -18331,7 +19302,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>75</v>
+        <v>205</v>
       </c>
       <c r="C221">
         <v>818</v>
@@ -18411,7 +19382,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>33</v>
+        <v>206</v>
       </c>
       <c r="C222">
         <v>627</v>
@@ -18491,7 +19462,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>37</v>
+        <v>207</v>
       </c>
       <c r="C223">
         <v>702</v>
@@ -18571,7 +19542,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>76</v>
+        <v>208</v>
       </c>
       <c r="C224">
         <v>843</v>
@@ -18651,7 +19622,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>76</v>
+        <v>209</v>
       </c>
       <c r="C225">
         <v>505</v>
@@ -18731,7 +19702,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>30</v>
+        <v>210</v>
       </c>
       <c r="C226">
         <v>522</v>
@@ -18811,7 +19782,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>30</v>
+        <v>211</v>
       </c>
       <c r="C227">
         <v>609</v>
@@ -18891,7 +19862,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>77</v>
+        <v>212</v>
       </c>
       <c r="C228">
         <v>1065</v>
@@ -18971,7 +19942,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>37</v>
+        <v>213</v>
       </c>
       <c r="C229">
         <v>949</v>
@@ -19051,7 +20022,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>78</v>
+        <v>214</v>
       </c>
       <c r="C230">
         <v>1119</v>
@@ -19131,7 +20102,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>37</v>
+        <v>215</v>
       </c>
       <c r="C231">
         <v>831</v>
@@ -19211,7 +20182,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>37</v>
+        <v>216</v>
       </c>
       <c r="C232">
         <v>930</v>
@@ -19291,7 +20262,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>37</v>
+        <v>217</v>
       </c>
       <c r="C233">
         <v>1018</v>
@@ -19371,7 +20342,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>79</v>
+        <v>218</v>
       </c>
       <c r="C234">
         <v>911</v>
@@ -19451,7 +20422,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>79</v>
+        <v>219</v>
       </c>
       <c r="C235">
         <v>579</v>
@@ -19531,7 +20502,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>31</v>
+        <v>220</v>
       </c>
       <c r="C236">
         <v>724</v>
@@ -19611,7 +20582,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>80</v>
+        <v>221</v>
       </c>
       <c r="C237">
         <v>929</v>
@@ -19691,7 +20662,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>30</v>
+        <v>221</v>
       </c>
       <c r="C238">
         <v>1082</v>
@@ -19771,7 +20742,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>81</v>
+        <v>222</v>
       </c>
       <c r="C239">
         <v>737</v>
@@ -19851,7 +20822,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>81</v>
+        <v>223</v>
       </c>
       <c r="C240">
         <v>742</v>
@@ -19931,7 +20902,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>24</v>
+        <v>224</v>
       </c>
       <c r="C241">
         <v>963</v>
@@ -20011,7 +20982,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>82</v>
+        <v>225</v>
       </c>
       <c r="C242">
         <v>697</v>
@@ -20091,7 +21062,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>83</v>
+        <v>226</v>
       </c>
       <c r="C243">
         <v>346</v>
@@ -20171,7 +21142,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>24</v>
+        <v>227</v>
       </c>
       <c r="C244">
         <v>1112</v>
@@ -20251,7 +21222,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>24</v>
+        <v>228</v>
       </c>
       <c r="C245">
         <v>453</v>
@@ -20331,7 +21302,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>24</v>
+        <v>229</v>
       </c>
       <c r="C246">
         <v>748</v>
@@ -20411,7 +21382,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>33</v>
+        <v>230</v>
       </c>
       <c r="C247">
         <v>674</v>
@@ -20491,7 +21462,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>33</v>
+        <v>231</v>
       </c>
       <c r="C248">
         <v>541</v>
@@ -20571,7 +21542,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>24</v>
+        <v>232</v>
       </c>
       <c r="C249">
         <v>628</v>
@@ -20651,7 +21622,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>31</v>
+        <v>233</v>
       </c>
       <c r="C250">
         <v>663</v>
@@ -20731,7 +21702,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>84</v>
+        <v>234</v>
       </c>
       <c r="C251">
         <v>818</v>
@@ -20811,7 +21782,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>85</v>
+        <v>235</v>
       </c>
       <c r="C252">
         <v>842</v>
@@ -20891,7 +21862,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>85</v>
+        <v>236</v>
       </c>
       <c r="C253">
         <v>509</v>
@@ -20971,7 +21942,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>33</v>
+        <v>214</v>
       </c>
       <c r="C254">
         <v>610</v>
@@ -21051,7 +22022,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>86</v>
+        <v>237</v>
       </c>
       <c r="C255">
         <v>555</v>
@@ -21131,7 +22102,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>86</v>
+        <v>238</v>
       </c>
       <c r="C256">
         <v>594</v>
@@ -21211,7 +22182,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>24</v>
+        <v>239</v>
       </c>
       <c r="C257">
         <v>618</v>
@@ -21291,7 +22262,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>24</v>
+        <v>239</v>
       </c>
       <c r="C258">
         <v>608</v>
@@ -21371,7 +22342,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>33</v>
+        <v>240</v>
       </c>
       <c r="C259">
         <v>887</v>
@@ -21451,7 +22422,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>33</v>
+        <v>241</v>
       </c>
       <c r="C260">
         <v>795</v>
@@ -21531,7 +22502,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>31</v>
+        <v>242</v>
       </c>
       <c r="C261">
         <v>888</v>
@@ -21611,7 +22582,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>87</v>
+        <v>243</v>
       </c>
       <c r="C262">
         <v>626</v>
@@ -21691,7 +22662,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>31</v>
+        <v>244</v>
       </c>
       <c r="C263">
         <v>584</v>
@@ -21771,7 +22742,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>31</v>
+        <v>245</v>
       </c>
       <c r="C264">
         <v>558</v>
@@ -21851,7 +22822,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>24</v>
+        <v>246</v>
       </c>
       <c r="C265">
         <v>976</v>
@@ -21931,7 +22902,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>88</v>
+        <v>247</v>
       </c>
       <c r="C266">
         <v>846</v>
@@ -22011,7 +22982,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>30</v>
+        <v>248</v>
       </c>
       <c r="C267">
         <v>1081</v>
@@ -22091,7 +23062,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>31</v>
+        <v>249</v>
       </c>
       <c r="C268">
         <v>567</v>
@@ -22171,7 +23142,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>38</v>
+        <v>249</v>
       </c>
       <c r="C269">
         <v>702</v>
@@ -22251,7 +23222,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>24</v>
+        <v>250</v>
       </c>
       <c r="C270">
         <v>0</v>
@@ -22331,7 +23302,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>24</v>
+        <v>250</v>
       </c>
       <c r="C271">
         <v>528</v>
@@ -22411,7 +23382,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>89</v>
+        <v>250</v>
       </c>
       <c r="C272">
         <v>794</v>
@@ -22491,7 +23462,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>89</v>
+        <v>251</v>
       </c>
       <c r="C273">
         <v>581</v>
@@ -22571,7 +23542,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>89</v>
+        <v>252</v>
       </c>
       <c r="C274">
         <v>1181</v>
@@ -22651,7 +23622,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>90</v>
+        <v>252</v>
       </c>
       <c r="C275">
         <v>974</v>
@@ -22731,7 +23702,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>90</v>
+        <v>252</v>
       </c>
       <c r="C276">
         <v>970</v>
@@ -22811,7 +23782,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>90</v>
+        <v>253</v>
       </c>
       <c r="C277">
         <v>920</v>
@@ -22891,7 +23862,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>90</v>
+        <v>253</v>
       </c>
       <c r="C278">
         <v>805</v>
@@ -22971,7 +23942,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>24</v>
+        <v>253</v>
       </c>
       <c r="C279">
         <v>958</v>
@@ -23051,7 +24022,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>91</v>
+        <v>254</v>
       </c>
       <c r="C280">
         <v>746</v>
@@ -23131,7 +24102,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>91</v>
+        <v>255</v>
       </c>
       <c r="C281">
         <v>611</v>
@@ -23211,7 +24182,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>91</v>
+        <v>256</v>
       </c>
       <c r="C282">
         <v>643</v>
@@ -23291,7 +24262,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>91</v>
+        <v>257</v>
       </c>
       <c r="C283">
         <v>714</v>
@@ -23371,7 +24342,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>91</v>
+        <v>258</v>
       </c>
       <c r="C284">
         <v>1037</v>
@@ -23451,7 +24422,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>92</v>
+        <v>259</v>
       </c>
       <c r="C285">
         <v>1084</v>
@@ -23531,7 +24502,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>92</v>
+        <v>260</v>
       </c>
       <c r="C286">
         <v>965</v>
@@ -23611,7 +24582,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>92</v>
+        <v>261</v>
       </c>
       <c r="C287">
         <v>600</v>
@@ -23691,7 +24662,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>92</v>
+        <v>262</v>
       </c>
       <c r="C288">
         <v>713</v>
@@ -23771,7 +24742,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>30</v>
+        <v>263</v>
       </c>
       <c r="C289">
         <v>822</v>
@@ -23851,7 +24822,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>30</v>
+        <v>263</v>
       </c>
       <c r="C290">
         <v>434</v>
@@ -23931,7 +24902,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>11</v>
+        <v>263</v>
       </c>
       <c r="C291">
         <v>671</v>
@@ -24011,7 +24982,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>34</v>
+        <v>264</v>
       </c>
       <c r="C292">
         <v>735</v>
@@ -24091,7 +25062,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>34</v>
+        <v>265</v>
       </c>
       <c r="C293">
         <v>733</v>
@@ -24171,7 +25142,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>33</v>
+        <v>266</v>
       </c>
       <c r="C294">
         <v>602</v>
@@ -24251,7 +25222,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>9</v>
+        <v>266</v>
       </c>
       <c r="C295">
         <v>857</v>
@@ -24331,7 +25302,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>31</v>
+        <v>265</v>
       </c>
       <c r="C296">
         <v>1040</v>
@@ -24411,7 +25382,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>33</v>
+        <v>160</v>
       </c>
       <c r="C297">
         <v>612</v>
@@ -24491,7 +25462,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>30</v>
+        <v>267</v>
       </c>
       <c r="C298">
         <v>933</v>
@@ -24571,7 +25542,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>93</v>
+        <v>268</v>
       </c>
       <c r="C299">
         <v>650</v>
@@ -24651,7 +25622,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>93</v>
+        <v>269</v>
       </c>
       <c r="C300">
         <v>557</v>
@@ -24731,7 +25702,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>94</v>
+        <v>269</v>
       </c>
       <c r="C301">
         <v>751</v>
@@ -24811,7 +25782,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>94</v>
+        <v>256</v>
       </c>
       <c r="C302">
         <v>752</v>
@@ -24891,7 +25862,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>95</v>
+        <v>256</v>
       </c>
       <c r="C303">
         <v>702</v>
@@ -24971,7 +25942,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>95</v>
+        <v>270</v>
       </c>
       <c r="C304">
         <v>703</v>
@@ -25051,7 +26022,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>94</v>
+        <v>271</v>
       </c>
       <c r="C305">
         <v>1058</v>
@@ -25131,7 +26102,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>31</v>
+        <v>272</v>
       </c>
       <c r="C306">
         <v>697</v>
@@ -25211,7 +26182,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>31</v>
+        <v>273</v>
       </c>
       <c r="C307">
         <v>495</v>
@@ -25291,7 +26262,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>33</v>
+        <v>273</v>
       </c>
       <c r="C308">
         <v>831</v>
@@ -25371,7 +26342,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>33</v>
+        <v>274</v>
       </c>
       <c r="C309">
         <v>984</v>
@@ -25451,7 +26422,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>33</v>
+        <v>274</v>
       </c>
       <c r="C310">
         <v>654</v>
@@ -25531,7 +26502,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>33</v>
+        <v>275</v>
       </c>
       <c r="C311">
         <v>581</v>
@@ -25611,7 +26582,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>96</v>
+        <v>276</v>
       </c>
       <c r="C312">
         <v>533</v>
@@ -25691,7 +26662,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>30</v>
+        <v>277</v>
       </c>
       <c r="C313">
         <v>818</v>
@@ -25771,7 +26742,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>97</v>
+        <v>278</v>
       </c>
       <c r="C314">
         <v>794</v>
@@ -25851,7 +26822,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>37</v>
+        <v>234</v>
       </c>
       <c r="C315">
         <v>643</v>
@@ -25931,7 +26902,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>98</v>
+        <v>234</v>
       </c>
       <c r="C316">
         <v>783</v>
@@ -26011,7 +26982,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>98</v>
+        <v>279</v>
       </c>
       <c r="C317">
         <v>721</v>
@@ -26091,7 +27062,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>98</v>
+        <v>279</v>
       </c>
       <c r="C318">
         <v>563</v>
@@ -26171,7 +27142,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>31</v>
+        <v>280</v>
       </c>
       <c r="C319">
         <v>774</v>
@@ -26251,7 +27222,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>31</v>
+        <v>281</v>
       </c>
       <c r="C320">
         <v>0</v>
@@ -26331,7 +27302,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>99</v>
+        <v>282</v>
       </c>
       <c r="C321">
         <v>898</v>
@@ -26411,7 +27382,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>100</v>
+        <v>283</v>
       </c>
       <c r="C322">
         <v>843</v>
@@ -26491,7 +27462,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>33</v>
+        <v>283</v>
       </c>
       <c r="C323">
         <v>1042</v>
@@ -26571,7 +27542,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>31</v>
+        <v>284</v>
       </c>
       <c r="C324">
         <v>931</v>
@@ -26651,7 +27622,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>38</v>
+        <v>285</v>
       </c>
       <c r="C325">
         <v>1101</v>
@@ -26731,7 +27702,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>38</v>
+        <v>286</v>
       </c>
       <c r="C326">
         <v>1084</v>
@@ -26811,7 +27782,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>30</v>
+        <v>287</v>
       </c>
       <c r="C327">
         <v>1092</v>
@@ -26891,7 +27862,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>30</v>
+        <v>287</v>
       </c>
       <c r="C328">
         <v>879</v>
@@ -26971,7 +27942,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>101</v>
+        <v>288</v>
       </c>
       <c r="C329">
         <v>724</v>
@@ -27051,7 +28022,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>33</v>
+        <v>289</v>
       </c>
       <c r="C330">
         <v>906</v>
@@ -27131,7 +28102,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>33</v>
+        <v>289</v>
       </c>
       <c r="C331">
         <v>537</v>
@@ -27211,7 +28182,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>102</v>
+        <v>290</v>
       </c>
       <c r="C332">
         <v>1042</v>
@@ -27291,7 +28262,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>31</v>
+        <v>291</v>
       </c>
       <c r="C333">
         <v>895</v>
@@ -27371,7 +28342,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>31</v>
+        <v>292</v>
       </c>
       <c r="C334">
         <v>912</v>
@@ -27451,7 +28422,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>67</v>
+        <v>293</v>
       </c>
       <c r="C335">
         <v>781</v>
@@ -27531,7 +28502,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>103</v>
+        <v>294</v>
       </c>
       <c r="C336">
         <v>869</v>
@@ -27611,7 +28582,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>103</v>
+        <v>295</v>
       </c>
       <c r="C337">
         <v>729</v>
@@ -27691,7 +28662,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>104</v>
+        <v>296</v>
       </c>
       <c r="C338">
         <v>905</v>
@@ -27771,7 +28742,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>104</v>
+        <v>297</v>
       </c>
       <c r="C339">
         <v>775</v>
@@ -27851,7 +28822,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>105</v>
+        <v>298</v>
       </c>
       <c r="C340">
         <v>796</v>
@@ -27931,7 +28902,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>106</v>
+        <v>299</v>
       </c>
       <c r="C341">
         <v>737</v>
@@ -28011,7 +28982,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>106</v>
+        <v>300</v>
       </c>
       <c r="C342">
         <v>675</v>
@@ -28091,7 +29062,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>31</v>
+        <v>300</v>
       </c>
       <c r="C343">
         <v>1043</v>
@@ -28171,7 +29142,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>31</v>
+        <v>301</v>
       </c>
       <c r="C344">
         <v>536</v>
@@ -28251,7 +29222,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>4</v>
+        <v>302</v>
       </c>
       <c r="C345">
         <v>1066</v>
@@ -28331,7 +29302,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>4</v>
+        <v>303</v>
       </c>
       <c r="C346">
         <v>990</v>
@@ -28411,7 +29382,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>24</v>
+        <v>304</v>
       </c>
       <c r="C347">
         <v>1124</v>
@@ -28491,7 +29462,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>24</v>
+        <v>305</v>
       </c>
       <c r="C348">
         <v>702</v>
@@ -28571,7 +29542,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>33</v>
+        <v>306</v>
       </c>
       <c r="C349">
         <v>463</v>
@@ -28651,7 +29622,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>41</v>
+        <v>234</v>
       </c>
       <c r="C350">
         <v>1050</v>
@@ -28731,7 +29702,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>41</v>
+        <v>307</v>
       </c>
       <c r="C351">
         <v>1088</v>
@@ -28811,7 +29782,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>31</v>
+        <v>188</v>
       </c>
       <c r="C352">
         <v>954</v>
@@ -28891,7 +29862,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>31</v>
+        <v>308</v>
       </c>
       <c r="C353">
         <v>359</v>
@@ -28971,7 +29942,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C354">
         <v>1010</v>
@@ -29051,7 +30022,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>107</v>
+        <v>309</v>
       </c>
       <c r="C355">
         <v>826</v>
@@ -29131,7 +30102,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>31</v>
+        <v>310</v>
       </c>
       <c r="C356">
         <v>622</v>
@@ -29211,7 +30182,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>31</v>
+        <v>311</v>
       </c>
       <c r="C357">
         <v>508</v>
@@ -29291,7 +30262,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>38</v>
+        <v>256</v>
       </c>
       <c r="C358">
         <v>736</v>
@@ -29371,7 +30342,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>37</v>
+        <v>312</v>
       </c>
       <c r="C359">
         <v>751</v>
@@ -29451,7 +30422,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>24</v>
+        <v>312</v>
       </c>
       <c r="C360">
         <v>1128</v>
@@ -29531,7 +30502,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>37</v>
+        <v>313</v>
       </c>
       <c r="C361">
         <v>911</v>
@@ -29611,7 +30582,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>37</v>
+        <v>313</v>
       </c>
       <c r="C362">
         <v>787</v>
@@ -29691,7 +30662,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>108</v>
+        <v>314</v>
       </c>
       <c r="C363">
         <v>983</v>
@@ -29771,7 +30742,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>108</v>
+        <v>315</v>
       </c>
       <c r="C364">
         <v>864</v>
@@ -29851,7 +30822,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>109</v>
+        <v>316</v>
       </c>
       <c r="C365">
         <v>702</v>
@@ -29931,7 +30902,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>109</v>
+        <v>317</v>
       </c>
       <c r="C366">
         <v>698</v>
@@ -30011,7 +30982,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>30</v>
+        <v>318</v>
       </c>
       <c r="C367">
         <v>714</v>
@@ -30091,7 +31062,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>37</v>
+        <v>319</v>
       </c>
       <c r="C368">
         <v>766</v>
@@ -30171,7 +31142,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>30</v>
+        <v>320</v>
       </c>
       <c r="C369">
         <v>394</v>
@@ -30251,7 +31222,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>30</v>
+        <v>321</v>
       </c>
       <c r="C370">
         <v>812</v>
@@ -30331,7 +31302,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>30</v>
+        <v>322</v>
       </c>
       <c r="C371">
         <v>579</v>
@@ -30411,7 +31382,7 @@
         <v>370</v>
       </c>
       <c r="B372" t="s">
-        <v>24</v>
+        <v>323</v>
       </c>
       <c r="C372">
         <v>930</v>
@@ -30491,7 +31462,7 @@
         <v>371</v>
       </c>
       <c r="B373" t="s">
-        <v>24</v>
+        <v>324</v>
       </c>
       <c r="C373">
         <v>490</v>
@@ -30571,7 +31542,7 @@
         <v>372</v>
       </c>
       <c r="B374" t="s">
-        <v>110</v>
+        <v>325</v>
       </c>
       <c r="C374">
         <v>675</v>
@@ -30651,7 +31622,7 @@
         <v>373</v>
       </c>
       <c r="B375" t="s">
-        <v>3</v>
+        <v>326</v>
       </c>
       <c r="C375">
         <v>492</v>
@@ -30731,7 +31702,7 @@
         <v>374</v>
       </c>
       <c r="B376" t="s">
-        <v>31</v>
+        <v>327</v>
       </c>
       <c r="C376">
         <v>612</v>
@@ -30811,7 +31782,7 @@
         <v>375</v>
       </c>
       <c r="B377" t="s">
-        <v>33</v>
+        <v>328</v>
       </c>
       <c r="C377">
         <v>603</v>
@@ -30891,7 +31862,7 @@
         <v>376</v>
       </c>
       <c r="B378" t="s">
-        <v>105</v>
+        <v>329</v>
       </c>
       <c r="C378">
         <v>1062</v>
@@ -30971,7 +31942,7 @@
         <v>377</v>
       </c>
       <c r="B379" t="s">
-        <v>30</v>
+        <v>330</v>
       </c>
       <c r="C379">
         <v>834</v>
@@ -31051,7 +32022,7 @@
         <v>378</v>
       </c>
       <c r="B380" t="s">
-        <v>31</v>
+        <v>331</v>
       </c>
       <c r="C380">
         <v>872</v>
@@ -31131,7 +32102,7 @@
         <v>379</v>
       </c>
       <c r="B381" t="s">
-        <v>33</v>
+        <v>332</v>
       </c>
       <c r="C381">
         <v>592</v>
@@ -31211,7 +32182,7 @@
         <v>380</v>
       </c>
       <c r="B382" t="s">
-        <v>31</v>
+        <v>333</v>
       </c>
       <c r="C382">
         <v>850</v>
@@ -31291,7 +32262,7 @@
         <v>381</v>
       </c>
       <c r="B383" t="s">
-        <v>111</v>
+        <v>334</v>
       </c>
       <c r="C383">
         <v>697</v>
@@ -31371,7 +32342,7 @@
         <v>382</v>
       </c>
       <c r="B384" t="s">
-        <v>38</v>
+        <v>335</v>
       </c>
       <c r="C384">
         <v>872</v>
@@ -31451,7 +32422,7 @@
         <v>383</v>
       </c>
       <c r="B385" t="s">
-        <v>38</v>
+        <v>336</v>
       </c>
       <c r="C385">
         <v>699</v>
@@ -31531,7 +32502,7 @@
         <v>384</v>
       </c>
       <c r="B386" t="s">
-        <v>44</v>
+        <v>337</v>
       </c>
       <c r="C386">
         <v>632</v>
@@ -31611,7 +32582,7 @@
         <v>385</v>
       </c>
       <c r="B387" t="s">
-        <v>24</v>
+        <v>338</v>
       </c>
       <c r="C387">
         <v>692</v>
@@ -31691,7 +32662,7 @@
         <v>386</v>
       </c>
       <c r="B388" t="s">
-        <v>110</v>
+        <v>339</v>
       </c>
       <c r="C388">
         <v>956</v>
@@ -31771,7 +32742,7 @@
         <v>387</v>
       </c>
       <c r="B389" t="s">
-        <v>31</v>
+        <v>340</v>
       </c>
       <c r="C389">
         <v>873</v>
@@ -31851,7 +32822,7 @@
         <v>388</v>
       </c>
       <c r="B390" t="s">
-        <v>37</v>
+        <v>341</v>
       </c>
       <c r="C390">
         <v>1043</v>
@@ -31931,7 +32902,7 @@
         <v>389</v>
       </c>
       <c r="B391" t="s">
-        <v>37</v>
+        <v>342</v>
       </c>
       <c r="C391">
         <v>931</v>
@@ -32011,7 +32982,7 @@
         <v>390</v>
       </c>
       <c r="B392" t="s">
-        <v>24</v>
+        <v>343</v>
       </c>
       <c r="C392">
         <v>658</v>
@@ -32091,7 +33062,7 @@
         <v>391</v>
       </c>
       <c r="B393" t="s">
-        <v>24</v>
+        <v>344</v>
       </c>
       <c r="C393">
         <v>958</v>
@@ -32171,7 +33142,7 @@
         <v>392</v>
       </c>
       <c r="B394" t="s">
-        <v>24</v>
+        <v>345</v>
       </c>
       <c r="C394">
         <v>947</v>
@@ -32251,7 +33222,7 @@
         <v>393</v>
       </c>
       <c r="B395" t="s">
-        <v>112</v>
+        <v>346</v>
       </c>
       <c r="C395">
         <v>824</v>
@@ -32331,7 +33302,7 @@
         <v>394</v>
       </c>
       <c r="B396" t="s">
-        <v>112</v>
+        <v>347</v>
       </c>
       <c r="C396">
         <v>716</v>
@@ -32411,7 +33382,7 @@
         <v>395</v>
       </c>
       <c r="B397" t="s">
-        <v>30</v>
+        <v>348</v>
       </c>
       <c r="C397">
         <v>1114</v>
@@ -32491,7 +33462,7 @@
         <v>396</v>
       </c>
       <c r="B398" t="s">
-        <v>30</v>
+        <v>349</v>
       </c>
       <c r="C398">
         <v>1095</v>
@@ -32571,7 +33542,7 @@
         <v>397</v>
       </c>
       <c r="B399" t="s">
-        <v>11</v>
+        <v>350</v>
       </c>
       <c r="C399">
         <v>1018</v>
@@ -32651,7 +33622,7 @@
         <v>398</v>
       </c>
       <c r="B400" t="s">
-        <v>26</v>
+        <v>351</v>
       </c>
       <c r="C400">
         <v>994</v>
@@ -32731,7 +33702,7 @@
         <v>399</v>
       </c>
       <c r="B401" t="s">
-        <v>26</v>
+        <v>352</v>
       </c>
       <c r="C401">
         <v>914</v>
@@ -32811,7 +33782,7 @@
         <v>400</v>
       </c>
       <c r="B402" t="s">
-        <v>9</v>
+        <v>353</v>
       </c>
       <c r="C402">
         <v>638</v>
@@ -32891,7 +33862,7 @@
         <v>401</v>
       </c>
       <c r="B403" t="s">
-        <v>34</v>
+        <v>354</v>
       </c>
       <c r="C403">
         <v>635</v>
@@ -32971,7 +33942,7 @@
         <v>402</v>
       </c>
       <c r="B404" t="s">
-        <v>34</v>
+        <v>355</v>
       </c>
       <c r="C404">
         <v>635</v>
@@ -33051,7 +34022,7 @@
         <v>403</v>
       </c>
       <c r="B405" t="s">
-        <v>9</v>
+        <v>356</v>
       </c>
       <c r="C405">
         <v>496</v>
@@ -33131,7 +34102,7 @@
         <v>404</v>
       </c>
       <c r="B406" t="s">
-        <v>9</v>
+        <v>357</v>
       </c>
       <c r="C406">
         <v>1069</v>
@@ -33211,7 +34182,7 @@
         <v>405</v>
       </c>
       <c r="B407" t="s">
-        <v>113</v>
+        <v>358</v>
       </c>
       <c r="C407">
         <v>855</v>
@@ -33291,7 +34262,7 @@
         <v>406</v>
       </c>
       <c r="B408" t="s">
-        <v>16</v>
+        <v>359</v>
       </c>
       <c r="C408">
         <v>580</v>
@@ -33371,7 +34342,7 @@
         <v>407</v>
       </c>
       <c r="B409" t="s">
-        <v>114</v>
+        <v>360</v>
       </c>
       <c r="C409">
         <v>652</v>
@@ -33451,7 +34422,7 @@
         <v>408</v>
       </c>
       <c r="B410" t="s">
-        <v>114</v>
+        <v>361</v>
       </c>
       <c r="C410">
         <v>1182</v>
@@ -33531,7 +34502,7 @@
         <v>409</v>
       </c>
       <c r="B411" t="s">
-        <v>26</v>
+        <v>362</v>
       </c>
       <c r="C411">
         <v>724</v>
@@ -33611,7 +34582,7 @@
         <v>410</v>
       </c>
       <c r="B412" t="s">
-        <v>26</v>
+        <v>363</v>
       </c>
       <c r="C412">
         <v>529</v>
@@ -33691,7 +34662,7 @@
         <v>411</v>
       </c>
       <c r="B413" t="s">
-        <v>31</v>
+        <v>364</v>
       </c>
       <c r="C413">
         <v>1067</v>
@@ -33771,7 +34742,7 @@
         <v>412</v>
       </c>
       <c r="B414" t="s">
-        <v>115</v>
+        <v>365</v>
       </c>
       <c r="C414">
         <v>585</v>
@@ -33851,7 +34822,7 @@
         <v>413</v>
       </c>
       <c r="B415" t="s">
-        <v>16</v>
+        <v>366</v>
       </c>
       <c r="C415">
         <v>543</v>
@@ -33931,7 +34902,7 @@
         <v>414</v>
       </c>
       <c r="B416" t="s">
-        <v>16</v>
+        <v>367</v>
       </c>
       <c r="C416">
         <v>684</v>
@@ -34011,7 +34982,7 @@
         <v>415</v>
       </c>
       <c r="B417" t="s">
-        <v>34</v>
+        <v>368</v>
       </c>
       <c r="C417">
         <v>421</v>
@@ -34091,7 +35062,7 @@
         <v>416</v>
       </c>
       <c r="B418" t="s">
-        <v>34</v>
+        <v>369</v>
       </c>
       <c r="C418">
         <v>1125</v>
@@ -34171,7 +35142,7 @@
         <v>417</v>
       </c>
       <c r="B419" t="s">
-        <v>16</v>
+        <v>370</v>
       </c>
       <c r="C419">
         <v>567</v>
@@ -34251,7 +35222,7 @@
         <v>418</v>
       </c>
       <c r="B420" t="s">
-        <v>11</v>
+        <v>371</v>
       </c>
       <c r="C420">
         <v>613</v>
@@ -34331,7 +35302,7 @@
         <v>419</v>
       </c>
       <c r="B421" t="s">
-        <v>28</v>
+        <v>372</v>
       </c>
       <c r="C421">
         <v>828</v>
@@ -34411,7 +35382,7 @@
         <v>420</v>
       </c>
       <c r="B422" t="s">
-        <v>10</v>
+        <v>373</v>
       </c>
       <c r="C422">
         <v>860</v>
@@ -34491,7 +35462,7 @@
         <v>421</v>
       </c>
       <c r="B423" t="s">
-        <v>9</v>
+        <v>374</v>
       </c>
       <c r="C423">
         <v>664</v>
@@ -34571,7 +35542,7 @@
         <v>422</v>
       </c>
       <c r="B424" t="s">
-        <v>9</v>
+        <v>375</v>
       </c>
       <c r="C424">
         <v>512</v>
@@ -34651,7 +35622,7 @@
         <v>423</v>
       </c>
       <c r="B425" t="s">
-        <v>9</v>
+        <v>376</v>
       </c>
       <c r="C425">
         <v>1098</v>
@@ -34731,7 +35702,7 @@
         <v>424</v>
       </c>
       <c r="B426" t="s">
-        <v>9</v>
+        <v>377</v>
       </c>
       <c r="C426">
         <v>0</v>
@@ -34811,7 +35782,7 @@
         <v>425</v>
       </c>
       <c r="B427" t="s">
-        <v>16</v>
+        <v>378</v>
       </c>
       <c r="C427">
         <v>972</v>
@@ -34891,7 +35862,7 @@
         <v>426</v>
       </c>
       <c r="B428" t="s">
-        <v>116</v>
+        <v>379</v>
       </c>
       <c r="C428">
         <v>828</v>
@@ -34971,7 +35942,7 @@
         <v>427</v>
       </c>
       <c r="B429" t="s">
-        <v>116</v>
+        <v>380</v>
       </c>
       <c r="C429">
         <v>758</v>
@@ -35051,7 +36022,7 @@
         <v>428</v>
       </c>
       <c r="B430" t="s">
-        <v>72</v>
+        <v>381</v>
       </c>
       <c r="C430">
         <v>615</v>
@@ -35131,7 +36102,7 @@
         <v>429</v>
       </c>
       <c r="B431" t="s">
-        <v>79</v>
+        <v>382</v>
       </c>
       <c r="C431">
         <v>888</v>
@@ -35211,7 +36182,7 @@
         <v>430</v>
       </c>
       <c r="B432" t="s">
-        <v>117</v>
+        <v>383</v>
       </c>
       <c r="C432">
         <v>590</v>
@@ -35291,7 +36262,7 @@
         <v>431</v>
       </c>
       <c r="B433" t="s">
-        <v>9</v>
+        <v>384</v>
       </c>
       <c r="C433">
         <v>919</v>
@@ -35371,7 +36342,7 @@
         <v>432</v>
       </c>
       <c r="B434" t="s">
-        <v>118</v>
+        <v>385</v>
       </c>
       <c r="C434">
         <v>891</v>
@@ -35451,7 +36422,7 @@
         <v>433</v>
       </c>
       <c r="B435" t="s">
-        <v>119</v>
+        <v>386</v>
       </c>
       <c r="C435">
         <v>827</v>
@@ -35531,7 +36502,7 @@
         <v>434</v>
       </c>
       <c r="B436" t="s">
-        <v>10</v>
+        <v>387</v>
       </c>
       <c r="C436">
         <v>918</v>
@@ -35611,7 +36582,7 @@
         <v>435</v>
       </c>
       <c r="B437" t="s">
-        <v>10</v>
+        <v>388</v>
       </c>
       <c r="C437">
         <v>966</v>
@@ -35691,7 +36662,7 @@
         <v>436</v>
       </c>
       <c r="B438" t="s">
-        <v>10</v>
+        <v>389</v>
       </c>
       <c r="C438">
         <v>827</v>
@@ -35771,7 +36742,7 @@
         <v>437</v>
       </c>
       <c r="B439" t="s">
-        <v>76</v>
+        <v>390</v>
       </c>
       <c r="C439">
         <v>992</v>
@@ -35851,7 +36822,7 @@
         <v>438</v>
       </c>
       <c r="B440" t="s">
-        <v>16</v>
+        <v>391</v>
       </c>
       <c r="C440">
         <v>1044</v>
@@ -35931,7 +36902,7 @@
         <v>439</v>
       </c>
       <c r="B441" t="s">
-        <v>16</v>
+        <v>392</v>
       </c>
       <c r="C441">
         <v>1102</v>
@@ -36011,7 +36982,7 @@
         <v>440</v>
       </c>
       <c r="B442" t="s">
-        <v>120</v>
+        <v>393</v>
       </c>
       <c r="C442">
         <v>1008</v>
@@ -36091,7 +37062,7 @@
         <v>441</v>
       </c>
       <c r="B443" t="s">
-        <v>120</v>
+        <v>394</v>
       </c>
       <c r="C443">
         <v>729</v>
@@ -36171,7 +37142,7 @@
         <v>442</v>
       </c>
       <c r="B444" t="s">
-        <v>121</v>
+        <v>395</v>
       </c>
       <c r="C444">
         <v>547</v>
@@ -36251,7 +37222,7 @@
         <v>443</v>
       </c>
       <c r="B445" t="s">
-        <v>122</v>
+        <v>396</v>
       </c>
       <c r="C445">
         <v>845</v>
@@ -36331,7 +37302,7 @@
         <v>444</v>
       </c>
       <c r="B446" t="s">
-        <v>34</v>
+        <v>397</v>
       </c>
       <c r="C446">
         <v>844</v>
@@ -36411,7 +37382,7 @@
         <v>445</v>
       </c>
       <c r="B447" t="s">
-        <v>34</v>
+        <v>398</v>
       </c>
       <c r="C447">
         <v>1005</v>
@@ -36491,7 +37462,7 @@
         <v>446</v>
       </c>
       <c r="B448" t="s">
-        <v>120</v>
+        <v>399</v>
       </c>
       <c r="C448">
         <v>534</v>
@@ -36571,7 +37542,7 @@
         <v>447</v>
       </c>
       <c r="B449" t="s">
-        <v>16</v>
+        <v>400</v>
       </c>
       <c r="C449">
         <v>871</v>
@@ -36651,7 +37622,7 @@
         <v>448</v>
       </c>
       <c r="B450" t="s">
-        <v>16</v>
+        <v>401</v>
       </c>
       <c r="C450">
         <v>329</v>
@@ -36731,7 +37702,7 @@
         <v>449</v>
       </c>
       <c r="B451" t="s">
-        <v>123</v>
+        <v>402</v>
       </c>
       <c r="C451">
         <v>1011</v>
@@ -36811,7 +37782,7 @@
         <v>450</v>
       </c>
       <c r="B452" t="s">
-        <v>123</v>
+        <v>403</v>
       </c>
       <c r="C452">
         <v>0</v>
@@ -36891,7 +37862,7 @@
         <v>451</v>
       </c>
       <c r="B453" t="s">
-        <v>123</v>
+        <v>404</v>
       </c>
       <c r="C453">
         <v>1080</v>
@@ -36971,7 +37942,7 @@
         <v>452</v>
       </c>
       <c r="B454" t="s">
-        <v>123</v>
+        <v>405</v>
       </c>
       <c r="C454">
         <v>1050</v>
@@ -37051,7 +38022,7 @@
         <v>453</v>
       </c>
       <c r="B455" t="s">
-        <v>124</v>
+        <v>406</v>
       </c>
       <c r="C455">
         <v>1083</v>
@@ -37131,7 +38102,7 @@
         <v>454</v>
       </c>
       <c r="B456" t="s">
-        <v>124</v>
+        <v>407</v>
       </c>
       <c r="C456">
         <v>1009</v>
@@ -37211,7 +38182,7 @@
         <v>455</v>
       </c>
       <c r="B457" t="s">
-        <v>125</v>
+        <v>408</v>
       </c>
       <c r="C457">
         <v>1058</v>
@@ -37291,7 +38262,7 @@
         <v>456</v>
       </c>
       <c r="B458" t="s">
-        <v>125</v>
+        <v>409</v>
       </c>
       <c r="C458">
         <v>1021</v>
@@ -37371,7 +38342,7 @@
         <v>457</v>
       </c>
       <c r="B459" t="s">
-        <v>125</v>
+        <v>410</v>
       </c>
       <c r="C459">
         <v>673</v>
@@ -37451,7 +38422,7 @@
         <v>458</v>
       </c>
       <c r="B460" t="s">
-        <v>116</v>
+        <v>411</v>
       </c>
       <c r="C460">
         <v>853</v>
@@ -37531,7 +38502,7 @@
         <v>459</v>
       </c>
       <c r="B461" t="s">
-        <v>116</v>
+        <v>412</v>
       </c>
       <c r="C461">
         <v>779</v>
@@ -37611,7 +38582,7 @@
         <v>460</v>
       </c>
       <c r="B462" t="s">
-        <v>126</v>
+        <v>413</v>
       </c>
       <c r="C462">
         <v>392</v>
@@ -37691,7 +38662,7 @@
         <v>461</v>
       </c>
       <c r="B463" t="s">
-        <v>17</v>
+        <v>414</v>
       </c>
       <c r="C463">
         <v>741</v>
@@ -37771,7 +38742,7 @@
         <v>462</v>
       </c>
       <c r="B464" t="s">
-        <v>17</v>
+        <v>415</v>
       </c>
       <c r="C464">
         <v>738</v>
@@ -37851,7 +38822,7 @@
         <v>463</v>
       </c>
       <c r="B465" t="s">
-        <v>12</v>
+        <v>416</v>
       </c>
       <c r="C465">
         <v>500</v>
@@ -37931,7 +38902,7 @@
         <v>464</v>
       </c>
       <c r="B466" t="s">
-        <v>127</v>
+        <v>417</v>
       </c>
       <c r="C466">
         <v>868</v>
